--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35629000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33624000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32354000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28655000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25075000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19621000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14975000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12894000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12554000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12336000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11387000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11395000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11461000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11486000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12540000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16098000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16926000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17916000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18224000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18170000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17836000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16965000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16369000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -951,8 +957,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1052,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1277,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,8 +1372,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1412,8 +1434,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
@@ -1430,23 +1452,26 @@
       <c r="AA15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22787000</v>
+      </c>
+      <c r="E17" s="3">
         <v>20479000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19321000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15138000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11486000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6754000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3054000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1352000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>655000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>618000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-467000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-662000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2061000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2329000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2809000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5129000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5727000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6508000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6892000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6808000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6237000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5620000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5368000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12842000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13145000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13033000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13517000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13589000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12867000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11921000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11542000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11899000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11718000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11854000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12057000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9400000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9157000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9731000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10969000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11199000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11408000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11332000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11362000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11599000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11345000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11001000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,192 +1726,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9718000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5050000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4999000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4428000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3651000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8612000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8544000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9592000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8399000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8792000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7383000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8373000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8313000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9423000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8511000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9627000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6606000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5022000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4247000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4963000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8608000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7297000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9393000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9185000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9222000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9509000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9011000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,192 +2009,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3124000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8095000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8034000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9089000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7897000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8301000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6892000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7879000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7818000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8950000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8042000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9166000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6119000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4546000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3799000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4531000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8169000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6859000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8959000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8767000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8698000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8994000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8498000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E24" s="3">
         <v>293000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>626000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>928000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>765000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1219000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>645000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>812000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>805000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1259000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1116000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>649000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-335000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>266000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>521000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1175000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1082000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1611000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1456000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1420000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1714000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7802000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7408000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8161000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7132000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7082000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6247000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7067000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7013000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7691000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9224000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8050000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5470000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4881000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3533000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4010000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6994000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5777000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7348000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7311000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7278000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7167000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6784000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2838000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7270000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7102000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7656000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6904000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6579000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5932000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6600000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6773000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7260000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8964000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7560000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5208000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4440000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3284000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3541000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6748000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5272000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7109000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6869000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7039000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6701000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6466000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2578,8 +2638,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2596,12 +2656,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9718000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5050000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4999000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4428000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5692000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4566000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5029000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3663000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4081000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2768000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3812000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2891000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3281000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4611000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5932000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6438000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3030000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4549000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2373000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2595000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2901000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2351000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2503000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2838000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7270000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7102000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7656000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6904000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6579000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5932000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6600000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6773000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7260000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8964000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7560000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5208000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4440000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3284000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3541000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6748000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5272000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7109000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6869000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7039000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6701000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6466000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2838000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7270000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7102000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7656000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6904000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6579000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5932000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6600000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6773000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7260000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8964000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7560000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5208000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4440000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3284000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3541000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6748000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5272000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7109000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6869000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7039000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6701000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6466000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,192 +3416,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>333073000</v>
+      </c>
+      <c r="E41" s="3">
         <v>351726000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>373553000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>376218000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>230203000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>204976000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>198002000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>273934000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>348221000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>279854000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>260030000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>326101000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>380463000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>301006000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>289346000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>250390000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>161560000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>157094000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>171394000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>171623000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>177404000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>184858000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>171199000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>605647000</v>
+      </c>
+      <c r="E42" s="3">
         <v>671117000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>642097000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>665640000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>619583000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>648110000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>635345000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>669384000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>540288000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>597847000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>609181000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>589785000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>556637000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>631630000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>728899000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>565229000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>552015000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>587959000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>553668000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>557950000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>526698000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>520837000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>483328000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3607,8 +3699,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3699,8 +3794,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3791,8 +3889,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3883,8 +3984,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3975,100 +4079,106 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21005000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21008000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21036000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21235000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21265000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20860000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20979000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21040000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21066000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20775000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20777000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20476000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21000000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20802000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33690000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20892000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20261000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20293000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20326000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19851000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9906000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9680000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9537000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4079,7 +4189,7 @@
         <v>71021000</v>
       </c>
       <c r="F49" s="3">
-        <v>71122000</v>
+        <v>71021000</v>
       </c>
       <c r="G49" s="3">
         <v>71122000</v>
@@ -4094,31 +4204,31 @@
         <v>71122000</v>
       </c>
       <c r="K49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="L49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>71223000</v>
       </c>
       <c r="M49" s="3">
         <v>71223000</v>
       </c>
       <c r="N49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="O49" s="3">
         <v>71051000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>70551000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>70551000</v>
       </c>
       <c r="R49" s="3">
         <v>70551000</v>
       </c>
       <c r="S49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="T49" s="3">
         <v>70651000</v>
@@ -4130,37 +4240,40 @@
         <v>70651000</v>
       </c>
       <c r="W49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="X49" s="3">
         <v>72525000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>70859000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>70993000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,8 +4459,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4427,16 +4546,19 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3180151000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,8 +4816,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4779,47 +4909,50 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>336972000</v>
+      </c>
+      <c r="E58" s="3">
         <v>344069000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>337479000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>380626000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>238258000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>237843000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>237482000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>246843000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>224926000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>229253000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>243549000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>236733000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4829,142 +4962,148 @@
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>210955000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>237369000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>233390000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>205510000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>228704000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>207527000</v>
+      </c>
+      <c r="E59" s="3">
         <v>206492000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>205736000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>216621000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>224073000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>224615000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>214522000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>219625000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200419000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>191572000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>184607000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>193563000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>181799000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>175960000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>175302000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>183029000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>182798000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>172286000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>168658000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>173681000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165026000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>170138000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>152010000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5055,100 +5194,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>275391000</v>
+      </c>
+      <c r="E61" s="3">
         <v>282262000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>277059000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>273012000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>259610000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>267368000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>269623000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>270553000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>270983000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>276282000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>265883000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>235050000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>260968000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>255616000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>261530000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>253601000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>216602000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>236167000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>238011000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>233929000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>229392000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>211842000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>201531000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5239,8 +5384,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2888505000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5843,31 +6010,31 @@
         <v>28397000</v>
       </c>
       <c r="H70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="I70" s="3">
         <v>29134000</v>
       </c>
       <c r="J70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="K70" s="3">
         <v>27137000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="L70" s="3">
-        <v>23441000</v>
       </c>
       <c r="M70" s="3">
         <v>23441000</v>
       </c>
       <c r="N70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="O70" s="3">
         <v>24319000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="P70" s="3">
-        <v>23427000</v>
       </c>
       <c r="Q70" s="3">
         <v>23427000</v>
@@ -5876,16 +6043,16 @@
         <v>23427000</v>
       </c>
       <c r="S70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="T70" s="3">
         <v>23401000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>23606000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="V70" s="3">
-        <v>22326000</v>
       </c>
       <c r="W70" s="3">
         <v>22326000</v>
@@ -5894,19 +6061,19 @@
         <v>22326000</v>
       </c>
       <c r="Y70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="Z70" s="3">
         <v>23181000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AB70" s="3">
         <v>22323000</v>
       </c>
       <c r="AC70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AD70" s="3">
         <v>25220000</v>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>25220000</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>25220000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>224672000</v>
+      </c>
+      <c r="E72" s="3">
         <v>223749000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>218397000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>213062000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>207003000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>201957000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>197159000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>192929000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>188064000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>183007000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>177499000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>170082000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>164088000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>160447000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>157578000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>155866000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>156319000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>151183000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>147577000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>141888000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>136314000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>130747000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>125546000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>263249000</v>
+      </c>
+      <c r="E76" s="3">
         <v>258667000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>254922000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>251799000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>244800000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>240390000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>239984000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>239480000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>245358000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>249023000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>253678000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>249681000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>248414000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>245423000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>242210000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>241491000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>241409000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>244781000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>246719000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>244684000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>242999000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>239832000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>241035000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2838000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7270000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7102000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7656000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6904000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6579000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5932000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6600000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6773000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7260000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8964000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7560000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5208000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4440000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3284000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3541000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6748000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5272000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7109000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6869000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7039000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6701000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6466000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E83" s="3">
         <v>517000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>510000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>503000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>502000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>491000</v>
       </c>
       <c r="I83" s="3">
         <v>491000</v>
       </c>
       <c r="J83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="K83" s="3">
         <v>494000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>495000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>473000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>469000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>461000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>487000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>476000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>448000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>432000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>439000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>438000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>434000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>418000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>524000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>515000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>513000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>511000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>515000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>523000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>531000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>534000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>549000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>32724000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11772000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11786000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30998000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13154000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44651000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9795000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>54594000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>19043000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>59103000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15101000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>19606000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,8 +7681,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7554,8 +7774,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64183000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>57884000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>30846000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>14380000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>34761000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>16738000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>54977000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1980000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,100 +8096,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1927000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1879000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1785000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1847000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-464000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,280 +8474,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11291000</v>
+      </c>
+      <c r="E100" s="3">
         <v>27628000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>126121000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40886000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>83040000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>43663000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>51320000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>113627000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>77938000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>129132000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>161147000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>22828000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7923000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>30556000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>21045000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1515000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-640000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>348000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4234000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-417000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-936000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>526000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>807000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1719000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1179000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-949000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>508000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1024000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-607000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>229000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-710000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>700000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>227000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>414000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>651000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>813000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18653000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>146015000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25227000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6974000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>68367000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19824000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>79457000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11660000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38956000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>88830000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4466000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-229000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13659000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,217 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36285000</v>
+      </c>
+      <c r="E8" s="3">
         <v>35629000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33624000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32354000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28655000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25075000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19621000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14975000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12894000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12554000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12336000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11387000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11395000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11461000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11486000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12540000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16098000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16926000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17916000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18224000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18170000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17836000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16965000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -960,8 +966,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1064,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,8 +1394,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1437,8 +1459,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1455,23 +1477,26 @@
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23572000</v>
+      </c>
+      <c r="E17" s="3">
         <v>22787000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>20479000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19321000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15138000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11486000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6754000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3054000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1352000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>655000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>618000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-467000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-662000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2061000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2329000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2809000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5129000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5727000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6508000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6892000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6808000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6237000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5620000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12713000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12842000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13145000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13033000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13517000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13589000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12867000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11921000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11542000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11899000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11718000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11854000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12057000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9400000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9157000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9731000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10969000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11199000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11408000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11332000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11362000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11599000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11345000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,198 +1759,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5451000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9718000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5050000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4999000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4428000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7800000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3651000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8612000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8544000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9592000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8399000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8792000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7383000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8373000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8313000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9423000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8511000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9627000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6606000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5022000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4247000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4963000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8608000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7297000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9393000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9185000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9222000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9509000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2012,198 +2051,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7262000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3124000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8095000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8034000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9089000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7897000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8301000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6892000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7879000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7818000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8950000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8042000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9166000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6119000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4546000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3799000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4531000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8169000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6859000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8959000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8767000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8698000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8994000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>588000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-20000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>293000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>626000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>928000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>765000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1219000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>645000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>812000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>805000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1259000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1116000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>649000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-335000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>266000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>521000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1175000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1082000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1611000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1456000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1420000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1827000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6674000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3144000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7802000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7408000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8161000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7132000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7082000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6247000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7067000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7013000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7691000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9224000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8050000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5470000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4881000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3533000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4010000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6994000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5777000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7348000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7311000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7278000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7167000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6142000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2838000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7270000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7102000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7656000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6904000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6579000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5932000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6600000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6773000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7260000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8964000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7560000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5208000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4440000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3284000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3541000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6748000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5272000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7109000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6869000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7039000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6701000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2641,8 +2701,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2659,12 +2719,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5451000</v>
+      </c>
+      <c r="E32" s="3">
         <v>9718000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5050000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4999000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4428000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5692000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4566000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5029000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3663000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4081000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2768000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3812000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2891000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3281000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4611000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5932000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6438000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3030000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4549000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2373000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2595000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2901000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2351000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6142000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2838000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7270000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7102000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7656000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6904000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6579000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5932000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6600000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6773000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7260000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8964000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7560000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5208000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4440000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3284000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3541000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6748000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5272000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7109000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6869000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7039000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6701000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6142000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2838000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7270000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7102000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7656000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6904000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6579000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5932000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6600000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6773000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7260000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8964000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7560000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5208000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4440000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3284000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3541000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6748000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5272000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7109000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6869000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7039000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6701000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,198 +3502,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>313404000</v>
+      </c>
+      <c r="E41" s="3">
         <v>333073000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>351726000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>373553000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>376218000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>230203000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>204976000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>198002000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>273934000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>348221000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>279854000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>260030000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>326101000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>380463000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>301006000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>289346000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>250390000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>161560000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>157094000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>171394000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>171623000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>177404000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>184858000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>678552000</v>
+      </c>
+      <c r="E42" s="3">
         <v>605647000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>671117000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>642097000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>665640000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>619583000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>648110000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>635345000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>669384000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>540288000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>597847000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>609181000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>589785000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>556637000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>631630000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>728899000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>565229000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>552015000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>587959000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>553668000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>557950000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>526698000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>520837000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3702,8 +3794,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3797,8 +3892,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3892,8 +3990,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3987,8 +4088,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4082,103 +4186,109 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20889000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21005000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21008000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21036000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21235000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21265000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20860000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20979000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21040000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21066000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20775000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20777000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20476000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21000000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20802000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33690000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20892000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20261000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20293000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20326000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19851000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9906000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9680000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4192,7 +4302,7 @@
         <v>71021000</v>
       </c>
       <c r="G49" s="3">
-        <v>71122000</v>
+        <v>71021000</v>
       </c>
       <c r="H49" s="3">
         <v>71122000</v>
@@ -4207,31 +4317,31 @@
         <v>71122000</v>
       </c>
       <c r="L49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="M49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>71223000</v>
       </c>
       <c r="N49" s="3">
         <v>71223000</v>
       </c>
       <c r="O49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="P49" s="3">
         <v>71051000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>70551000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>70551000</v>
       </c>
       <c r="S49" s="3">
         <v>70551000</v>
       </c>
       <c r="T49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="U49" s="3">
         <v>70651000</v>
@@ -4243,37 +4353,40 @@
         <v>70651000</v>
       </c>
       <c r="X49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>72525000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>70859000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,8 +4578,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4549,16 +4668,19 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3273803000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,8 +4946,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4912,50 +5042,53 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>383133000</v>
+      </c>
+      <c r="E58" s="3">
         <v>336972000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>344069000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>337479000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>380626000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>238258000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>237843000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>237482000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>246843000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>224926000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>229253000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>243549000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>236733000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4965,145 +5098,151 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>210955000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>237369000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>233390000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>205510000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>214129000</v>
+      </c>
+      <c r="E59" s="3">
         <v>207527000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>206492000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>205736000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>216621000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>224073000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>224615000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>214522000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>219625000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200419000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>191572000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>184607000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>193563000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>181799000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>175960000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>175302000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>183029000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>182798000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>172286000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>168658000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>173681000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>165026000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>170138000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5197,103 +5336,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>274443000</v>
+      </c>
+      <c r="E61" s="3">
         <v>275391000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>282262000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>277059000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>273012000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>259610000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>267368000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>269623000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>270553000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>270983000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>276282000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>265883000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>235050000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>260968000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>255616000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>261530000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>253601000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>216602000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>236167000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>238011000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>233929000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>229392000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>211842000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5387,8 +5532,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2980251000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6013,31 +6180,31 @@
         <v>28397000</v>
       </c>
       <c r="I70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="J70" s="3">
         <v>29134000</v>
       </c>
       <c r="K70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="L70" s="3">
         <v>27137000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="M70" s="3">
-        <v>23441000</v>
       </c>
       <c r="N70" s="3">
         <v>23441000</v>
       </c>
       <c r="O70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="P70" s="3">
         <v>24319000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>23427000</v>
       </c>
       <c r="R70" s="3">
         <v>23427000</v>
@@ -6046,16 +6213,16 @@
         <v>23427000</v>
       </c>
       <c r="T70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="U70" s="3">
         <v>23401000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>23606000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="W70" s="3">
-        <v>22326000</v>
       </c>
       <c r="X70" s="3">
         <v>22326000</v>
@@ -6064,19 +6231,19 @@
         <v>22326000</v>
       </c>
       <c r="Z70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AA70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AC70" s="3">
         <v>22323000</v>
       </c>
       <c r="AD70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AE70" s="3">
         <v>25220000</v>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>25220000</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>25220000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>228902000</v>
+      </c>
+      <c r="E72" s="3">
         <v>224672000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>223749000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>218397000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>213062000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>207003000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>201957000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>197159000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>192929000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>188064000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>183007000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>177499000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>170082000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>164088000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>160447000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>157578000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>155866000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>156319000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>151183000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>147577000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>141888000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>136314000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>130747000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>265155000</v>
+      </c>
+      <c r="E76" s="3">
         <v>263249000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>258667000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>254922000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>251799000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>244800000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>240390000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>239984000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>239480000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>245358000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>249023000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>253678000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>249681000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>248414000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>245423000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>242210000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>241491000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>241409000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>244781000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>246719000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>244684000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>242999000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>239832000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6142000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2838000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7270000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7102000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7656000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6904000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6579000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5932000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6600000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6773000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7260000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8964000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7560000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5208000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4440000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3284000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3541000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6748000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5272000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7109000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6869000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7039000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6701000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>538000</v>
+      </c>
+      <c r="E83" s="3">
         <v>527000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>517000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>510000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>503000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>502000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>491000</v>
       </c>
       <c r="J83" s="3">
         <v>491000</v>
       </c>
       <c r="K83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="L83" s="3">
         <v>494000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>495000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>473000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>469000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>461000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>487000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>476000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>448000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>432000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>439000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>438000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>434000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>418000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>524000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>515000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>513000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>511000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>515000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>523000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>531000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>534000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>549000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15539000</v>
+      </c>
+      <c r="E89" s="3">
         <v>32724000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11772000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11786000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30998000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13154000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44651000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9795000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>54594000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19043000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>59103000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15101000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>19606000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,8 +7901,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7777,8 +7997,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-71322000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>57884000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>30846000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>14380000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>34761000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>16738000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>54977000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,103 +8329,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1987000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1927000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1879000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1785000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1847000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-464000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,289 +8719,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>68658000</v>
+      </c>
+      <c r="E100" s="3">
         <v>11291000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>27628000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>126121000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40886000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>83040000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>43663000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>51320000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>113627000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>77938000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>129132000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>161147000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>22828000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7923000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>30556000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>21045000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1466000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1515000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-640000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>348000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4234000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-417000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-936000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>526000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>807000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1719000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1179000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-949000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>508000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1024000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-607000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>229000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-710000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>700000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>227000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>414000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>651000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>813000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19669000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>146015000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25227000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6974000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>68367000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19824000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>79457000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11660000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38956000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>88830000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4466000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-229000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13659000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36854000</v>
+      </c>
+      <c r="E8" s="3">
         <v>36285000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35629000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33624000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32354000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28655000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25075000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19621000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14975000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12894000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12554000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12336000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11387000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11395000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11461000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11486000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12540000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16098000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16926000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17916000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18224000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18170000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17836000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -969,8 +975,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,8 +1076,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1416,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1462,8 +1484,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>5</v>
@@ -1480,23 +1502,26 @@
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24660000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23572000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22787000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20479000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19321000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15138000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11486000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6754000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3054000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1352000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>655000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>618000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-467000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-662000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2061000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2329000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2809000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5129000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5727000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6508000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6892000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6808000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6237000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12194000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12713000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12842000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13145000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13033000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13517000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13589000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12867000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11921000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11542000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11899000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11718000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11854000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12057000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9400000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9157000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9731000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10969000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11199000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11408000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11332000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11362000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11599000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,204 +1792,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4634000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5451000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9718000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5050000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4999000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4428000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8103000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7800000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3651000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8612000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8544000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9592000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8399000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8792000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7383000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8373000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8313000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9423000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8511000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9627000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6606000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5022000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4247000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4963000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8608000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7297000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9393000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9185000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9222000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2054,204 +2093,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7560000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7262000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3124000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8095000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8034000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9089000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7897000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8301000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6892000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7879000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7818000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8950000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8042000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9166000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6119000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4546000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3799000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4531000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8169000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6859000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8959000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8767000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8698000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>663000</v>
+      </c>
+      <c r="E24" s="3">
         <v>588000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-20000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>293000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>626000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>928000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>765000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1219000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>645000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>812000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>805000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1259000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1116000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>649000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-335000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>266000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>521000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1175000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1082000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1611000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1456000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6897000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6674000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3144000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7802000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7408000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8161000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7132000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7082000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6247000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7067000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7013000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7691000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9224000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8050000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5470000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4881000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3533000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4010000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6994000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5777000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7348000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7311000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7278000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6582000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6142000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2838000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7270000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7102000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7656000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6904000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6579000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5932000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6600000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6773000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7260000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8964000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7560000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5208000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4440000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3284000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3541000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6748000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5272000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7109000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6869000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>7039000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2704,8 +2764,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2722,12 +2782,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4634000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5451000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9718000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5050000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4999000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4428000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5692000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4566000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5029000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3663000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4081000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2768000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3812000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2891000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3281000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4611000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5932000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6438000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3030000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4549000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2373000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2595000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2901000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6582000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6142000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2838000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7270000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7102000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7656000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6904000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6579000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5932000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6600000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6773000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7260000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8964000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7560000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5208000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4440000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3284000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3541000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6748000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5272000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7109000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6869000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7039000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6582000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6142000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2838000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7270000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7102000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7656000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6904000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6579000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5932000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6600000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6773000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7260000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8964000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7560000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5208000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4440000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3284000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3541000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6748000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5272000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7109000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6869000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7039000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,204 +3588,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>320632000</v>
+      </c>
+      <c r="E41" s="3">
         <v>313404000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>333073000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>351726000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>373553000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>376218000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>230203000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>204976000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>198002000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>273934000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>348221000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>279854000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>260030000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>326101000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>380463000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>301006000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>289346000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>250390000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>161560000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>157094000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>171394000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>171623000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>177404000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>688543000</v>
+      </c>
+      <c r="E42" s="3">
         <v>678552000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>605647000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>671117000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>642097000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>665640000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>619583000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>648110000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>635345000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>669384000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>540288000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>597847000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>609181000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>589785000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>556637000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>631630000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>728899000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>565229000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>552015000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>587959000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>553668000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>557950000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>526698000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3797,8 +3889,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3895,8 +3990,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3993,8 +4091,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4091,8 +4192,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4189,106 +4293,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20624000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20889000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21005000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21008000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21036000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21235000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21265000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20860000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20979000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21040000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21066000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20775000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20777000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20476000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21000000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20802000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>33690000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20892000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20261000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20293000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20326000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19851000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9906000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4305,7 +4415,7 @@
         <v>71021000</v>
       </c>
       <c r="H49" s="3">
-        <v>71122000</v>
+        <v>71021000</v>
       </c>
       <c r="I49" s="3">
         <v>71122000</v>
@@ -4320,31 +4430,31 @@
         <v>71122000</v>
       </c>
       <c r="M49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="N49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>71223000</v>
       </c>
       <c r="O49" s="3">
         <v>71223000</v>
       </c>
       <c r="P49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>71051000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>70551000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>70551000</v>
       </c>
       <c r="T49" s="3">
         <v>70551000</v>
       </c>
       <c r="U49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="V49" s="3">
         <v>70651000</v>
@@ -4356,37 +4466,40 @@
         <v>70651000</v>
       </c>
       <c r="Y49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>72525000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,8 +4697,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4671,16 +4790,19 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3257996000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,8 +5076,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5045,53 +5175,56 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>414058000</v>
+      </c>
+      <c r="E58" s="3">
         <v>383133000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>336972000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>344069000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>337479000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>380626000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>238258000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>237843000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>237482000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>246843000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>224926000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>229253000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>243549000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>236733000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5101,148 +5234,154 @@
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>210955000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>237369000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>233390000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>213751000</v>
+      </c>
+      <c r="E59" s="3">
         <v>214129000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>207527000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>206492000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>205736000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>216621000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>224073000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>224615000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>214522000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>219625000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200419000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>191572000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>184607000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>193563000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>181799000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>175960000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>175302000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>183029000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>182798000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>172286000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>168658000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>173681000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>165026000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5339,106 +5478,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>276430000</v>
+      </c>
+      <c r="E61" s="3">
         <v>274443000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>275391000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>282262000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>277059000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>273012000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>259610000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>267368000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>269623000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>270553000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>270983000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>276282000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>265883000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>235050000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>260968000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>255616000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>261530000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>253601000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>216602000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>236167000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>238011000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>233929000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>229392000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5535,8 +5680,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2964104000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,13 +6323,16 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>28397000</v>
+        <v>26548000</v>
       </c>
       <c r="E70" s="3">
         <v>28397000</v>
@@ -6183,31 +6350,31 @@
         <v>28397000</v>
       </c>
       <c r="J70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="K70" s="3">
         <v>29134000</v>
       </c>
       <c r="L70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="M70" s="3">
         <v>27137000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="N70" s="3">
-        <v>23441000</v>
       </c>
       <c r="O70" s="3">
         <v>23441000</v>
       </c>
       <c r="P70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="Q70" s="3">
         <v>24319000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="R70" s="3">
-        <v>23427000</v>
       </c>
       <c r="S70" s="3">
         <v>23427000</v>
@@ -6216,16 +6383,16 @@
         <v>23427000</v>
       </c>
       <c r="U70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="V70" s="3">
         <v>23401000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>23606000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="X70" s="3">
-        <v>22326000</v>
       </c>
       <c r="Y70" s="3">
         <v>22326000</v>
@@ -6234,19 +6401,19 @@
         <v>22326000</v>
       </c>
       <c r="AA70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AB70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AD70" s="3">
         <v>22323000</v>
       </c>
       <c r="AE70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AF70" s="3">
         <v>25220000</v>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>25220000</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>25220000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>233597000</v>
+      </c>
+      <c r="E72" s="3">
         <v>228902000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>224672000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>223749000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>218397000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>213062000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>207003000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>201957000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>197159000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>192929000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>188064000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>183007000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>177499000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>170082000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>164088000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>160447000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>157578000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>155866000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>156319000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>151183000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>147577000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>141888000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>136314000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>267344000</v>
+      </c>
+      <c r="E76" s="3">
         <v>265155000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>263249000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>258667000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>254922000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>251799000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>244800000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>240390000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>239984000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>239480000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>245358000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>249023000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>253678000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>249681000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>248414000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>245423000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>242210000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>241491000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>241409000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>244781000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>246719000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>244684000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>242999000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6582000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6142000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2838000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7270000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7102000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7656000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6904000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6579000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5932000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6600000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6773000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7260000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8964000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7560000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5208000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4440000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3284000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3541000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6748000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5272000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7109000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6869000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7039000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>543000</v>
+      </c>
+      <c r="E83" s="3">
         <v>538000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>527000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>517000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>510000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>503000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>502000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>491000</v>
       </c>
       <c r="K83" s="3">
         <v>491000</v>
       </c>
       <c r="L83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="M83" s="3">
         <v>494000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>495000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>473000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>469000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>461000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>487000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>476000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>448000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>432000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>439000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>438000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>434000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>418000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>524000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>515000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>513000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>511000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>515000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>523000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>531000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>534000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>549000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18096000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32724000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11772000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11786000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30998000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13154000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44651000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9795000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>54594000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>19043000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>59103000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15101000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,8 +8121,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8000,8 +8220,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1523000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>57884000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>30846000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14380000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>34761000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>16738000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>54977000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,106 +8562,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1906000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1987000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1927000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1879000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1785000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1847000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-464000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,298 +8964,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8300000</v>
+      </c>
+      <c r="E100" s="3">
         <v>68658000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11291000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>27628000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>126121000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40886000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>83040000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>43663000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>51320000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>113627000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>77938000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>129132000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>161147000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>22828000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7923000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>30556000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1045000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1466000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1515000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-640000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>348000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4234000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-417000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-936000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>526000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>807000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1719000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1179000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-949000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>508000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1024000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-607000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>229000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>700000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>227000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>414000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>651000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>813000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7228000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>146015000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25227000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6974000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>68367000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19824000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>79457000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11660000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38956000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>88830000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4466000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-229000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,229 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>36854000</v>
+        <v>23803000</v>
       </c>
       <c r="E8" s="3">
-        <v>36285000</v>
+        <v>23869000</v>
       </c>
       <c r="F8" s="3">
-        <v>35629000</v>
+        <v>24499000</v>
       </c>
       <c r="G8" s="3">
-        <v>33624000</v>
+        <v>22455000</v>
       </c>
       <c r="H8" s="3">
-        <v>32354000</v>
+        <v>23933000</v>
       </c>
       <c r="I8" s="3">
-        <v>28655000</v>
+        <v>24072000</v>
       </c>
       <c r="J8" s="3">
+        <v>25327000</v>
+      </c>
+      <c r="K8" s="3">
         <v>25075000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19621000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14975000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12894000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12554000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12336000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11387000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11395000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11461000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11486000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12540000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16098000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16926000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17916000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18224000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18170000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17836000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -978,31 +984,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>23803000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>23869000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>24499000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>22455000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>23933000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>24072000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>25327000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1079,8 +1088,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,31 +1334,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>3700000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1419,31 +1438,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>549000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>543000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>538000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>527000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>517000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>510000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>503000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1487,8 +1509,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>5</v>
@@ -1505,23 +1527,26 @@
       <c r="AD15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>24660000</v>
+        <v>16479000</v>
       </c>
       <c r="E17" s="3">
-        <v>23572000</v>
+        <v>16309000</v>
       </c>
       <c r="F17" s="3">
-        <v>22787000</v>
+        <v>17237000</v>
       </c>
       <c r="G17" s="3">
-        <v>20479000</v>
+        <v>15631000</v>
       </c>
       <c r="H17" s="3">
-        <v>19321000</v>
+        <v>15838000</v>
       </c>
       <c r="I17" s="3">
-        <v>15138000</v>
+        <v>16038000</v>
       </c>
       <c r="J17" s="3">
+        <v>16238000</v>
+      </c>
+      <c r="K17" s="3">
         <v>11486000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6754000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3054000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1352000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>655000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>618000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-467000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-662000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2061000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2329000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2809000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5129000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5727000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6508000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6892000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6808000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6237000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12194000</v>
+        <v>7324000</v>
       </c>
       <c r="E18" s="3">
-        <v>12713000</v>
+        <v>7560000</v>
       </c>
       <c r="F18" s="3">
-        <v>12842000</v>
+        <v>7262000</v>
       </c>
       <c r="G18" s="3">
-        <v>13145000</v>
+        <v>6824000</v>
       </c>
       <c r="H18" s="3">
-        <v>13033000</v>
+        <v>8095000</v>
       </c>
       <c r="I18" s="3">
-        <v>13517000</v>
+        <v>8034000</v>
       </c>
       <c r="J18" s="3">
+        <v>9089000</v>
+      </c>
+      <c r="K18" s="3">
         <v>13589000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12867000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11921000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11542000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11899000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11718000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11854000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12057000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9400000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9157000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9731000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10969000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11199000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11408000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11332000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11362000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11599000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,233 +1825,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-4634000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-5451000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-9718000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-5050000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-4999000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-4428000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7873000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8103000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7800000</v>
       </c>
-      <c r="F21" s="3">
-        <v>3651000</v>
-      </c>
       <c r="G21" s="3">
+        <v>7351000</v>
+      </c>
+      <c r="H21" s="3">
         <v>8612000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8544000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9592000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8399000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8792000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7383000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8373000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8313000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9423000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8511000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9627000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6606000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5022000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4247000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4963000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8608000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7297000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9393000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9185000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9222000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2096,210 +2135,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7324000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7560000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7262000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3124000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8095000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8034000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9089000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7897000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8301000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6892000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7879000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7818000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8950000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8042000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9166000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6119000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4546000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3799000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4531000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8169000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6859000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8959000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8767000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8698000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E24" s="3">
         <v>663000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>588000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>293000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>626000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>928000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>765000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1219000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>645000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>812000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>805000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1259000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1116000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>649000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-335000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>266000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>521000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1175000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1082000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1611000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1456000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6896000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6897000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6674000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3144000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7802000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7408000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8161000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7132000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7082000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6247000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7067000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7013000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7691000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9224000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8050000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5470000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4881000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3533000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4010000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6994000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5777000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7348000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7311000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7278000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6380000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6582000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6142000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2838000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7270000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7102000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7656000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6904000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6579000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5932000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6600000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6773000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7260000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8964000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7560000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5208000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4440000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3284000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3541000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6748000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5272000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7109000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6869000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7039000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2767,8 +2827,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2785,12 +2845,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>4634000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>5451000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>9718000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>5050000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>4999000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>4428000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>5692000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4566000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5029000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3663000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4081000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2768000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3812000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2891000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3281000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4611000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5932000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6438000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3030000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4549000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2373000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2595000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2901000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6582000</v>
+        <v>6896000</v>
       </c>
       <c r="E33" s="3">
-        <v>6142000</v>
+        <v>6897000</v>
       </c>
       <c r="F33" s="3">
-        <v>2838000</v>
+        <v>6674000</v>
       </c>
       <c r="G33" s="3">
-        <v>7270000</v>
+        <v>3144000</v>
       </c>
       <c r="H33" s="3">
-        <v>7102000</v>
+        <v>7802000</v>
       </c>
       <c r="I33" s="3">
-        <v>7656000</v>
+        <v>7408000</v>
       </c>
       <c r="J33" s="3">
+        <v>8161000</v>
+      </c>
+      <c r="K33" s="3">
         <v>6904000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6579000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5932000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6600000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6773000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7260000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8964000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7560000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5208000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4440000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3284000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3541000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6748000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5272000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7109000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6869000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7039000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6582000</v>
+        <v>6896000</v>
       </c>
       <c r="E35" s="3">
-        <v>6142000</v>
+        <v>6897000</v>
       </c>
       <c r="F35" s="3">
-        <v>2838000</v>
+        <v>6674000</v>
       </c>
       <c r="G35" s="3">
-        <v>7270000</v>
+        <v>3144000</v>
       </c>
       <c r="H35" s="3">
-        <v>7102000</v>
+        <v>7802000</v>
       </c>
       <c r="I35" s="3">
-        <v>7656000</v>
+        <v>7408000</v>
       </c>
       <c r="J35" s="3">
+        <v>8161000</v>
+      </c>
+      <c r="K35" s="3">
         <v>6904000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6579000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5932000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6600000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6773000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7260000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8964000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7560000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5208000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4440000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3284000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3541000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6748000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5272000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7109000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6869000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7039000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,233 +3674,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>320632000</v>
+        <v>288789000</v>
       </c>
       <c r="E41" s="3">
-        <v>313404000</v>
+        <v>315232000</v>
       </c>
       <c r="F41" s="3">
-        <v>333073000</v>
+        <v>308104000</v>
       </c>
       <c r="G41" s="3">
-        <v>351726000</v>
+        <v>327473000</v>
       </c>
       <c r="H41" s="3">
-        <v>373553000</v>
+        <v>345626000</v>
       </c>
       <c r="I41" s="3">
-        <v>376218000</v>
+        <v>368053000</v>
       </c>
       <c r="J41" s="3">
+        <v>369718000</v>
+      </c>
+      <c r="K41" s="3">
         <v>230203000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>204976000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>198002000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>273934000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>348221000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>279854000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>260030000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>326101000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>380463000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>301006000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>289346000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>250390000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>161560000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>157094000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>171394000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>171623000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>177404000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>688543000</v>
+        <v>538978000</v>
       </c>
       <c r="E42" s="3">
-        <v>678552000</v>
+        <v>535606000</v>
       </c>
       <c r="F42" s="3">
-        <v>605647000</v>
+        <v>522628000</v>
       </c>
       <c r="G42" s="3">
-        <v>671117000</v>
+        <v>473632000</v>
       </c>
       <c r="H42" s="3">
-        <v>642097000</v>
+        <v>515333000</v>
       </c>
       <c r="I42" s="3">
-        <v>665640000</v>
+        <v>488346000</v>
       </c>
       <c r="J42" s="3">
+        <v>523405000</v>
+      </c>
+      <c r="K42" s="3">
         <v>619583000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>648110000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>635345000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>669384000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>540288000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>597847000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>609181000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>589785000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>556637000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>631630000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>728899000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>565229000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>552015000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>587959000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>553668000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>557950000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>526698000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>86867000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>76478000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>81606000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>77381000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>70047000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>69900000</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>75902000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3892,31 +3984,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>218000</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>145000</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>93000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3993,31 +4088,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>186396000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>156237000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>158924000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>135315000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>158984000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>156949000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>145314000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4094,31 +4192,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1118241000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1096214000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>1085223000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>1025548000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1103774000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1095633000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1127765000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4195,31 +4296,34 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>911096000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>880023000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>927922000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>903235000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>795516000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>773100000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>812954000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4296,132 +4400,138 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20624000</v>
+        <v>12033000</v>
       </c>
       <c r="E48" s="3">
+        <v>11917000</v>
+      </c>
+      <c r="F48" s="3">
         <v>20889000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21005000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21008000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21036000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21235000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21265000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20860000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20979000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21040000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21066000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20775000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20777000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20476000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21000000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20802000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>33690000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20892000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20261000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20293000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20326000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19851000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9906000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>71021000</v>
+        <v>69021000</v>
       </c>
       <c r="E49" s="3">
-        <v>71021000</v>
+        <v>69021000</v>
       </c>
       <c r="F49" s="3">
-        <v>71021000</v>
+        <v>69021000</v>
       </c>
       <c r="G49" s="3">
-        <v>71021000</v>
+        <v>69021000</v>
       </c>
       <c r="H49" s="3">
-        <v>71021000</v>
+        <v>69021000</v>
       </c>
       <c r="I49" s="3">
-        <v>71122000</v>
+        <v>69021000</v>
       </c>
       <c r="J49" s="3">
-        <v>71122000</v>
+        <v>69022000</v>
       </c>
       <c r="K49" s="3">
         <v>71122000</v>
@@ -4433,31 +4543,31 @@
         <v>71122000</v>
       </c>
       <c r="N49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="O49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>71223000</v>
       </c>
       <c r="P49" s="3">
         <v>71223000</v>
       </c>
       <c r="Q49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="R49" s="3">
         <v>71051000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>70551000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>70551000</v>
       </c>
       <c r="U49" s="3">
         <v>70551000</v>
       </c>
       <c r="V49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="W49" s="3">
         <v>70651000</v>
@@ -4469,37 +4579,40 @@
         <v>70651000</v>
       </c>
       <c r="Z49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>72525000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,31 +4816,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>151353000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>157274000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>134805000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>106580000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>127909000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>126134000</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>129789000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4793,16 +4912,19 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AI52" s="3" t="s">
+      <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3324293000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3257996000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,31 +5206,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1930352000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>1910491000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>1946496000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>1923827000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>1884601000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>1877209000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1910402000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5178,56 +5308,59 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>414058000</v>
+        <v>495274000</v>
       </c>
       <c r="E58" s="3">
-        <v>383133000</v>
+        <v>472089000</v>
       </c>
       <c r="F58" s="3">
-        <v>336972000</v>
+        <v>440428000</v>
       </c>
       <c r="G58" s="3">
-        <v>344069000</v>
+        <v>398167000</v>
       </c>
       <c r="H58" s="3">
-        <v>337479000</v>
+        <v>393328000</v>
       </c>
       <c r="I58" s="3">
-        <v>380626000</v>
+        <v>391066000</v>
       </c>
       <c r="J58" s="3">
+        <v>420895000</v>
+      </c>
+      <c r="K58" s="3">
         <v>238258000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>237843000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>237482000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>246843000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>224926000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>229253000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>243549000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>236733000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5237,174 +5370,180 @@
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>210955000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>237369000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>233390000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>213751000</v>
+        <v>98316000</v>
       </c>
       <c r="E59" s="3">
-        <v>214129000</v>
+        <v>100345000</v>
       </c>
       <c r="F59" s="3">
-        <v>207527000</v>
+        <v>114326000</v>
       </c>
       <c r="G59" s="3">
-        <v>206492000</v>
+        <v>95530000</v>
       </c>
       <c r="H59" s="3">
-        <v>205736000</v>
+        <v>102820000</v>
       </c>
       <c r="I59" s="3">
-        <v>216621000</v>
+        <v>97818000</v>
       </c>
       <c r="J59" s="3">
+        <v>104445000</v>
+      </c>
+      <c r="K59" s="3">
         <v>224073000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>224615000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>214522000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>219625000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200419000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>191572000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>184607000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>193563000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>181799000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>175960000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>175302000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>183029000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>182798000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>172286000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>168658000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>173681000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>165026000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>2720761000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>2671973000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>2690866000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>2600349000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>2565686000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>2548220000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>2628052000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5481,132 +5620,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>276430000</v>
+        <v>304412000</v>
       </c>
       <c r="E61" s="3">
-        <v>274443000</v>
+        <v>289511000</v>
       </c>
       <c r="F61" s="3">
-        <v>275391000</v>
+        <v>286608000</v>
       </c>
       <c r="G61" s="3">
-        <v>282262000</v>
+        <v>283302000</v>
       </c>
       <c r="H61" s="3">
-        <v>277059000</v>
+        <v>296888000</v>
       </c>
       <c r="I61" s="3">
-        <v>273012000</v>
+        <v>288111000</v>
       </c>
       <c r="J61" s="3">
+        <v>284228000</v>
+      </c>
+      <c r="K61" s="3">
         <v>259610000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>267368000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>269623000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>270553000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>270983000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>276282000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>265883000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>235050000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>260968000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>255616000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>261530000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>253601000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>216602000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>236167000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>238011000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>233929000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>229392000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>2608000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2620000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>2777000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>3155000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3452000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>3548000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>2181000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5683,8 +5828,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3027781000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2964104000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,16 +6490,19 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>24554000</v>
+      </c>
+      <c r="E70" s="3">
         <v>26548000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>28397000</v>
       </c>
       <c r="F70" s="3">
         <v>28397000</v>
@@ -6353,31 +6520,31 @@
         <v>28397000</v>
       </c>
       <c r="K70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="L70" s="3">
         <v>29134000</v>
       </c>
       <c r="M70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="N70" s="3">
         <v>27137000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="O70" s="3">
-        <v>23441000</v>
       </c>
       <c r="P70" s="3">
         <v>23441000</v>
       </c>
       <c r="Q70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="R70" s="3">
         <v>24319000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="S70" s="3">
-        <v>23427000</v>
       </c>
       <c r="T70" s="3">
         <v>23427000</v>
@@ -6386,16 +6553,16 @@
         <v>23427000</v>
       </c>
       <c r="V70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="W70" s="3">
         <v>23401000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>23606000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>22326000</v>
       </c>
       <c r="Z70" s="3">
         <v>22326000</v>
@@ -6404,19 +6571,19 @@
         <v>22326000</v>
       </c>
       <c r="AB70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AC70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AE70" s="3">
         <v>22323000</v>
       </c>
       <c r="AF70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AG70" s="3">
         <v>25220000</v>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>25220000</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>25220000</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>237954000</v>
+      </c>
+      <c r="E72" s="3">
         <v>233597000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>228902000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>224672000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>223749000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>218397000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>213062000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>207003000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>201957000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>197159000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>192929000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>188064000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>183007000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>177499000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>170082000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>164088000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>160447000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>157578000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>155866000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>156319000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>151183000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>147577000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>141888000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>136314000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271958000</v>
+      </c>
+      <c r="E76" s="3">
         <v>267344000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>265155000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>263249000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>258667000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>254922000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>251799000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>244800000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>240390000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>239984000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>239480000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>245358000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>249023000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>253678000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>249681000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>248414000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>245423000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>242210000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>241491000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>241409000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>244781000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>246719000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>244684000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>242999000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6582000</v>
+        <v>6896000</v>
       </c>
       <c r="E81" s="3">
-        <v>6142000</v>
+        <v>6897000</v>
       </c>
       <c r="F81" s="3">
-        <v>2838000</v>
+        <v>6674000</v>
       </c>
       <c r="G81" s="3">
-        <v>7270000</v>
+        <v>3144000</v>
       </c>
       <c r="H81" s="3">
-        <v>7102000</v>
+        <v>7802000</v>
       </c>
       <c r="I81" s="3">
-        <v>7656000</v>
+        <v>7408000</v>
       </c>
       <c r="J81" s="3">
+        <v>8161000</v>
+      </c>
+      <c r="K81" s="3">
         <v>6904000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6579000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5932000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6600000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6773000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7260000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8964000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7560000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5208000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4440000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3284000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3541000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6748000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5272000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7109000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6869000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7039000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>543000</v>
+        <v>497000</v>
       </c>
       <c r="E83" s="3">
-        <v>538000</v>
+        <v>491000</v>
       </c>
       <c r="F83" s="3">
-        <v>527000</v>
+        <v>483000</v>
       </c>
       <c r="G83" s="3">
-        <v>517000</v>
+        <v>483000</v>
       </c>
       <c r="H83" s="3">
-        <v>510000</v>
+        <v>471000</v>
       </c>
       <c r="I83" s="3">
-        <v>503000</v>
+        <v>472000</v>
       </c>
       <c r="J83" s="3">
+        <v>474000</v>
+      </c>
+      <c r="K83" s="3">
         <v>502000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>491000</v>
       </c>
       <c r="L83" s="3">
         <v>491000</v>
       </c>
       <c r="M83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="N83" s="3">
         <v>494000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>495000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>473000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>469000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>461000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>487000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>476000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>448000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>432000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>439000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>438000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>434000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>418000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>524000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>515000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>513000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>511000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>515000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>523000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>531000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>534000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>549000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37276000</v>
+      </c>
+      <c r="E89" s="3">
         <v>18096000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32724000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11772000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11786000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30998000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13154000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44651000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9795000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>54594000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>19043000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>59103000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15101000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,31 +8341,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8223,8 +8443,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27258000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1523000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>57884000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>30846000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14380000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>34761000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>16738000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>54977000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-1906000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-1987000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-1927000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-1879000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-1785000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-1847000</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-464000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,307 +9209,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>36779000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8300000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>68658000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11291000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27628000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>126121000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40886000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>83040000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>43663000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>51320000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>113627000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>77938000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>129132000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>161147000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>22828000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7923000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>30556000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1045000</v>
+        <v>-1293000</v>
       </c>
       <c r="E101" s="3">
-        <v>-1466000</v>
+        <v>-640000</v>
       </c>
       <c r="F101" s="3">
-        <v>1515000</v>
+        <v>348000</v>
       </c>
       <c r="G101" s="3">
+        <v>4234000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-3052000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-2970000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-1335000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>4234000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-3052000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-2970000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-1335000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-417000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-936000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>526000</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-2581000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>807000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>1719000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>1179000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-949000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>508000</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="H101" s="3">
-        <v>-640000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>348000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>4234000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-3052000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-2970000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-1335000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-417000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-936000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>526000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-2581000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>807000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>1719000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1179000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-949000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>508000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-1293000</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1024000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-607000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>229000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>700000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>227000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>414000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>651000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>813000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-25043000</v>
+      </c>
+      <c r="E102" s="3">
         <v>7228000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>146015000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25227000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6974000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>68367000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19824000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>79457000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11660000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38956000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>88830000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4466000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-229000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,235 +656,241 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23895000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23803000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23869000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24499000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22455000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23933000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24072000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25327000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25075000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19621000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14975000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12894000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12554000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12336000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11387000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11395000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11461000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11486000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12540000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16098000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16926000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17916000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18224000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18170000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17836000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -987,35 +993,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>23895000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23803000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23869000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24499000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22455000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23933000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24072000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25327000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1091,8 +1100,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,8 +1353,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,20 +1370,20 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>3700000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1441,35 +1460,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E15" s="3">
         <v>549000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>543000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>538000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>527000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>517000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>510000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>503000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1512,8 +1534,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>5</v>
@@ -1530,23 +1552,26 @@
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16787000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16479000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16309000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17237000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15631000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15838000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16038000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16238000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11486000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6754000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3054000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1352000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>655000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>618000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-467000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-662000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2061000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2329000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2809000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5129000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5727000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6508000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6892000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6808000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6237000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7108000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7324000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7560000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7262000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6824000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8095000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8034000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9089000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13589000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12867000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11921000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11542000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11899000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11718000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11854000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12057000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9400000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9157000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9731000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10969000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11199000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11408000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11332000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11362000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11599000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1852,190 +1885,196 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7667000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7873000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8103000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7800000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7351000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8612000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8544000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9592000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8399000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8792000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7383000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8373000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8313000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9423000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8511000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9627000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6606000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5022000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4247000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4963000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8608000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7297000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9393000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9185000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9222000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,8 +2099,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2138,216 +2177,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7108000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7324000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7560000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7262000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3124000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8095000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8034000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9089000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7897000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8301000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6892000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7879000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7818000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8950000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8042000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9166000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6119000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4546000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3799000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4531000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8169000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6859000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8959000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8767000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8698000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>443000</v>
+      </c>
+      <c r="E24" s="3">
         <v>428000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>663000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>588000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-20000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>293000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>626000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>928000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>765000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1219000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>645000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>812000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>805000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1259000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1116000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>649000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-335000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>266000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>521000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1175000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1082000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1611000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1456000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6665000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6896000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6897000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6674000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3144000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7802000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7408000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8161000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7132000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7082000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6247000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7067000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7013000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7691000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9224000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8050000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5470000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4881000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3533000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4010000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6994000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5777000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7348000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7311000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7278000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6399000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6380000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6582000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6142000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2838000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7270000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7102000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7656000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6904000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6579000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5932000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6600000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6773000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7260000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8964000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7560000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5208000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4440000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3284000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3541000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6748000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5272000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>7109000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6869000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7039000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,8 +2890,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2848,12 +2908,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3100,190 +3169,196 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>5692000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4566000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5029000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3663000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4081000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2768000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3812000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2891000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3281000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4611000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5932000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6438000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3030000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4549000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2373000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2595000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2901000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6665000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6896000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6897000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6674000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3144000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7802000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7408000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8161000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6904000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6579000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5932000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6600000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6773000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7260000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8964000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7560000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5208000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4440000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3284000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3541000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6748000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5272000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7109000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6869000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7039000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6665000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6896000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6897000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6674000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3144000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7802000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7408000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8161000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6904000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6579000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5932000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6600000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6773000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7260000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8964000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7560000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5208000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4440000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3284000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3541000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6748000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5272000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7109000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6869000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7039000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,243 +3760,250 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>284014000</v>
+      </c>
+      <c r="E41" s="3">
         <v>288789000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>315232000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>308104000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>327473000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345626000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>368053000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>369718000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>230203000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>204976000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>198002000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>273934000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>348221000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>279854000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>260030000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>326101000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>380463000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>301006000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>289346000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>250390000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>161560000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>157094000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>171394000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>171623000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>177404000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>464861000</v>
+      </c>
+      <c r="E42" s="3">
         <v>538978000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>535606000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>522628000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>473632000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>515333000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>488346000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>523405000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>619583000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>648110000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>635345000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>669384000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>540288000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>597847000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>609181000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>589785000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>556637000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>631630000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>728899000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>565229000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>552015000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>587959000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>553668000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>557950000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>526698000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>77947000</v>
+      </c>
+      <c r="E43" s="3">
         <v>86867000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>76478000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>81606000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>77381000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>70047000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>69900000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>75902000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3987,35 +4079,38 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E44" s="3">
         <v>60000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>218000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>90000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>145000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>93000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>97000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>117000</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -4091,35 +4186,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>174628000</v>
+      </c>
+      <c r="E45" s="3">
         <v>186396000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>156237000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>158924000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>135315000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>158984000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>156949000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>145314000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4195,35 +4293,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1017240000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1118241000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1096214000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1085223000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1025548000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1103774000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1095633000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1127765000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4299,35 +4400,38 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>911096000</v>
+        <v>919022000</v>
       </c>
       <c r="E47" s="3">
+        <v>894896000</v>
+      </c>
+      <c r="F47" s="3">
         <v>880023000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>927922000</v>
       </c>
-      <c r="G47" s="3">
-        <v>903235000</v>
-      </c>
       <c r="H47" s="3">
+        <v>872984000</v>
+      </c>
+      <c r="I47" s="3">
         <v>795516000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>773100000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>812954000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4403,112 +4507,118 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20695000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12033000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11917000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20889000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21005000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21008000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21036000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21235000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21265000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20860000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20979000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21040000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21066000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20775000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20777000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20476000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21000000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20802000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>33690000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20892000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20261000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20293000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20326000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19851000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9906000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4531,10 +4641,10 @@
         <v>69021000</v>
       </c>
       <c r="J49" s="3">
+        <v>69021000</v>
+      </c>
+      <c r="K49" s="3">
         <v>69022000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>71122000</v>
       </c>
       <c r="L49" s="3">
         <v>71122000</v>
@@ -4546,31 +4656,31 @@
         <v>71122000</v>
       </c>
       <c r="O49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="P49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>71223000</v>
       </c>
       <c r="Q49" s="3">
         <v>71223000</v>
       </c>
       <c r="R49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="S49" s="3">
         <v>71051000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>70551000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>70551000</v>
       </c>
       <c r="V49" s="3">
         <v>70551000</v>
       </c>
       <c r="W49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="X49" s="3">
         <v>70651000</v>
@@ -4582,37 +4692,40 @@
         <v>70651000</v>
       </c>
       <c r="AA49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>72525000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,35 +4935,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>151353000</v>
+        <v>152946000</v>
       </c>
       <c r="E52" s="3">
+        <v>167553000</v>
+      </c>
+      <c r="F52" s="3">
         <v>157274000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>134805000</v>
       </c>
-      <c r="G52" s="3">
-        <v>106580000</v>
-      </c>
       <c r="H52" s="3">
+        <v>151203000</v>
+      </c>
+      <c r="I52" s="3">
         <v>127909000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>126134000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>129789000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4915,16 +5034,19 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
+      <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3261519000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3324293000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3257996000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,35 +5336,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1965467000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1930352000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1910491000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1946496000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1923827000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1884601000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1877209000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1910402000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5311,59 +5441,62 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>452470000</v>
+      </c>
+      <c r="E58" s="3">
         <v>495274000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>472089000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>440428000</v>
       </c>
-      <c r="G58" s="3">
-        <v>398167000</v>
-      </c>
       <c r="H58" s="3">
+        <v>369483000</v>
+      </c>
+      <c r="I58" s="3">
         <v>393328000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>391066000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>420895000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>238258000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>237843000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>237482000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>246843000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>224926000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>229253000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>243549000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>236733000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5373,181 +5506,187 @@
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>210955000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>237369000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>233390000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>92543000</v>
+      </c>
+      <c r="E59" s="3">
         <v>98316000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100345000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>114326000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>95530000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>102820000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>97818000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>104445000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>224073000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>224615000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>214522000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>219625000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200419000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>191572000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>184607000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>193563000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>181799000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>175960000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>175302000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>183029000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>182798000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>172286000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>168658000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>173681000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>165026000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2696684000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2720761000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2671973000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2690866000</v>
       </c>
-      <c r="G60" s="3">
-        <v>2600349000</v>
-      </c>
       <c r="H60" s="3">
+        <v>2571665000</v>
+      </c>
+      <c r="I60" s="3">
         <v>2565686000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2548220000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2628052000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5623,139 +5762,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>264977000</v>
+      </c>
+      <c r="E61" s="3">
         <v>304412000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>289511000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>286608000</v>
       </c>
-      <c r="G61" s="3">
-        <v>283302000</v>
-      </c>
       <c r="H61" s="3">
+        <v>311986000</v>
+      </c>
+      <c r="I61" s="3">
         <v>296888000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>288111000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>284228000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>259610000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>267368000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>269623000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>270553000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>270983000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>276282000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>265883000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>235050000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>260968000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>255616000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>261530000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>253601000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>216602000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>236167000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>238011000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>233929000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>229392000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2666000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2608000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2620000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2777000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3155000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3452000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3548000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2181000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5831,8 +5976,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2965960000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3027781000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2964104000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,19 +6657,22 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>23159000</v>
+      </c>
+      <c r="E70" s="3">
         <v>24554000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>26548000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>28397000</v>
       </c>
       <c r="G70" s="3">
         <v>28397000</v>
@@ -6523,31 +6690,31 @@
         <v>28397000</v>
       </c>
       <c r="L70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="M70" s="3">
         <v>29134000</v>
       </c>
       <c r="N70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="O70" s="3">
         <v>27137000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="P70" s="3">
-        <v>23441000</v>
       </c>
       <c r="Q70" s="3">
         <v>23441000</v>
       </c>
       <c r="R70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="S70" s="3">
         <v>24319000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="T70" s="3">
-        <v>23427000</v>
       </c>
       <c r="U70" s="3">
         <v>23427000</v>
@@ -6556,16 +6723,16 @@
         <v>23427000</v>
       </c>
       <c r="W70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="X70" s="3">
         <v>23401000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>23606000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>22326000</v>
       </c>
       <c r="AA70" s="3">
         <v>22326000</v>
@@ -6574,19 +6741,19 @@
         <v>22326000</v>
       </c>
       <c r="AC70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AD70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AF70" s="3">
         <v>22323000</v>
       </c>
       <c r="AG70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AH70" s="3">
         <v>25220000</v>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>25220000</v>
       </c>
+      <c r="AK70" s="3">
+        <v>25220000</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>242349000</v>
+      </c>
+      <c r="E72" s="3">
         <v>237954000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>233597000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>228902000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>224672000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>223749000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>218397000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>213062000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>207003000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>201957000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>197159000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>192929000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>188064000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>183007000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>177499000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>170082000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>164088000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>160447000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>157578000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>155866000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>156319000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>151183000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>147577000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>141888000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>136314000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>272400000</v>
+      </c>
+      <c r="E76" s="3">
         <v>271958000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>267344000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>265155000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>263249000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>258667000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>254922000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>251799000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>244800000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>240390000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>239984000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>239480000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>245358000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>249023000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>253678000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>249681000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>248414000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>245423000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>242210000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>241491000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>241409000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>244781000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>246719000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>244684000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>242999000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6665000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6896000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6897000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6674000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3144000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7802000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7408000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8161000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6904000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6579000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5932000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6600000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6773000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7260000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8964000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7560000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5208000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4440000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3284000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3541000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6748000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5272000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7109000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6869000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7039000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E83" s="3">
         <v>497000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>491000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>483000</v>
       </c>
       <c r="G83" s="3">
         <v>483000</v>
       </c>
       <c r="H83" s="3">
+        <v>483000</v>
+      </c>
+      <c r="I83" s="3">
         <v>471000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>472000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>474000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>502000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>491000</v>
       </c>
       <c r="M83" s="3">
         <v>491000</v>
       </c>
       <c r="N83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="O83" s="3">
         <v>494000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>495000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>473000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>469000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>461000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>487000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>476000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>448000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>432000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>439000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>438000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>434000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>418000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>524000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>515000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>513000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>511000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>515000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>523000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>531000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>534000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>549000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25914000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-37276000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18096000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32724000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11772000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11786000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30998000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13154000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44651000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9795000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>54594000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>19043000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>59103000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15101000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,8 +8561,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8368,8 +8588,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8446,8 +8666,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9410000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27258000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1523000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>57884000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>30846000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14380000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>34761000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>16738000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>54977000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,8 +9028,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8822,86 +9055,89 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-464000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,316 +9454,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-36768000</v>
+      </c>
+      <c r="E100" s="3">
         <v>36779000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8300000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>68658000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>11291000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27628000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>126121000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>40886000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>83040000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>43663000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>51320000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>113627000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>77938000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>129132000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>161147000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>22828000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7923000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>30556000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1515000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-640000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>348000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4234000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4234000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-417000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-936000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>526000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>807000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1719000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1179000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-949000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>508000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1024000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-607000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>229000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>700000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>227000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>414000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>651000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>813000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5475000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-25043000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7228000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>146015000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25227000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6974000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>68367000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19824000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>79457000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11660000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38956000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>88830000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4466000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-229000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,241 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25886000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23895000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23803000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23869000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24499000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22455000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23933000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24072000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25327000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25075000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19621000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14975000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12894000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12554000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12336000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11387000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11395000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11461000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11486000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12540000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16098000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16926000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17916000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18224000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18170000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17836000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -996,38 +1002,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25886000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23895000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23803000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23869000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24499000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22455000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23933000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24072000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25327000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,8 +1372,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1373,20 +1392,20 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>3700000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1463,38 +1482,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E15" s="3">
         <v>559000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>549000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>543000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>538000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>527000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>517000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>510000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>503000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1537,8 +1559,8 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
@@ -1555,23 +1577,26 @@
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17770000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16787000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16479000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16309000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17237000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15631000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15838000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16038000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16238000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11486000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6754000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3054000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1352000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>655000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>618000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-467000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-662000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2061000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2329000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2809000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5129000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5727000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6508000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6892000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6808000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6237000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8116000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7108000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7324000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7560000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7262000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6824000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8095000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8034000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9089000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13589000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12867000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11921000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11542000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11899000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11718000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11854000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12057000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9400000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9157000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9731000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10969000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11199000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11408000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11332000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11362000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11599000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,8 +1891,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1888,193 +1921,199 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8681000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7667000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7873000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8103000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7800000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7351000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8612000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8544000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9592000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8399000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8792000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7383000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8373000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8313000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9423000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8511000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9627000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6606000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5022000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4247000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4963000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8608000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7297000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9393000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9185000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9222000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,8 +2141,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2180,222 +2219,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8116000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7108000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7324000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7560000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7262000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3124000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8095000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8034000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9089000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7897000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8301000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6892000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7879000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7818000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8950000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8042000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9166000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6119000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4546000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3799000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4531000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8169000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6859000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8959000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8767000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8698000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>720000</v>
+      </c>
+      <c r="E24" s="3">
         <v>443000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>428000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>663000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>588000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-20000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>293000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>626000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>928000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>765000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1219000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>645000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>812000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>805000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1259000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1116000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>649000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-335000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>266000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>521000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1175000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1082000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1611000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1456000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7396000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6665000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6896000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6897000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6674000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3144000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7802000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7408000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8161000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7132000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7082000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6247000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7067000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7013000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7691000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9224000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8050000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5470000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4881000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3533000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4010000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6994000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5777000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7348000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7311000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7278000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6990000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6399000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6380000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6582000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6142000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2838000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7270000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7102000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7656000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6904000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6579000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5932000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6600000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6773000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7260000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8964000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7560000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5208000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4440000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3284000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3541000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6748000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5272000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7109000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6869000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7039000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2953,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2911,12 +2971,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3172,193 +3241,199 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>5692000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4566000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5029000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3663000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4081000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2768000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3812000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2891000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3281000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4611000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5932000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6438000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3030000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4549000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2373000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2595000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2901000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7396000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6665000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6896000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6897000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6674000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3144000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7802000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7408000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8161000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6904000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6579000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5932000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6600000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6773000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7260000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8964000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7560000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5208000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4440000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3284000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3541000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6748000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5272000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7109000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6869000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7039000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7396000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6665000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6896000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6897000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6674000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3144000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7802000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7408000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8161000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6904000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6579000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5932000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6600000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6773000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7260000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8964000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7560000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5208000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4440000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3284000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3541000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6748000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5272000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7109000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6869000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7039000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,252 +3846,259 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>267679000</v>
+      </c>
+      <c r="E41" s="3">
         <v>284014000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>288789000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>315232000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>308104000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>327473000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>345626000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>368053000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>369718000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>230203000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>204976000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>198002000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>273934000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>348221000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>279854000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>260030000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>326101000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>380463000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>301006000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>289346000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>250390000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>161560000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>157094000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>171394000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171623000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>177404000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>538712000</v>
+      </c>
+      <c r="E42" s="3">
         <v>464861000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>538978000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>535606000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>522628000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>473632000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>515333000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>488346000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>523405000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>619583000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>648110000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>635345000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>669384000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>540288000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>597847000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>609181000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>589785000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>556637000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>631630000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>728899000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>565229000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>552015000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>587959000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>553668000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>557950000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>526698000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>76029000</v>
+      </c>
+      <c r="E43" s="3">
         <v>77947000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>86867000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>76478000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>81606000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>77381000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>70047000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69900000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>75902000</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4082,38 +4174,41 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E44" s="3">
         <v>145000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>60000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>218000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>90000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>145000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>93000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>97000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>117000</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -4189,38 +4284,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>175555000</v>
+      </c>
+      <c r="E45" s="3">
         <v>174628000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>186396000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>156237000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>158924000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>135315000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>158984000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>156949000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>145314000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4296,38 +4394,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1070860000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1017240000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1118241000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1096214000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1085223000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1025548000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1103774000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1095633000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1127765000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4403,38 +4504,41 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>941479000</v>
+      </c>
+      <c r="E47" s="3">
         <v>919022000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>894896000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>880023000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>927922000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>872984000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>795516000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>773100000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>812954000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4510,115 +4614,121 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12151000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20695000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12033000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11917000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20889000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21005000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21008000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21036000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21235000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21265000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20860000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20979000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21040000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21066000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20775000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20777000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20476000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21000000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20802000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33690000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20892000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20261000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20293000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20326000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19851000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9906000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4644,10 +4754,10 @@
         <v>69021000</v>
       </c>
       <c r="K49" s="3">
+        <v>69021000</v>
+      </c>
+      <c r="L49" s="3">
         <v>69022000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>71122000</v>
       </c>
       <c r="M49" s="3">
         <v>71122000</v>
@@ -4659,31 +4769,31 @@
         <v>71122000</v>
       </c>
       <c r="P49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>71223000</v>
       </c>
       <c r="R49" s="3">
         <v>71223000</v>
       </c>
       <c r="S49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="T49" s="3">
         <v>71051000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>70551000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>70551000</v>
       </c>
       <c r="W49" s="3">
         <v>70551000</v>
       </c>
       <c r="X49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="Y49" s="3">
         <v>70651000</v>
@@ -4695,37 +4805,40 @@
         <v>70651000</v>
       </c>
       <c r="AB49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>72525000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,38 +5054,41 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>158544000</v>
+      </c>
+      <c r="E52" s="3">
         <v>152946000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>167553000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>157274000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>134805000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>151203000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>127909000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>126134000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>129789000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5037,16 +5156,19 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AK52" s="3" t="s">
+      <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3349424000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3261519000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3324293000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3257996000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,38 +5466,39 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1989564000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1965467000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1930352000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1910491000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1946496000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1923827000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1884601000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1877209000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1910402000</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5444,62 +5574,65 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>478451000</v>
+      </c>
+      <c r="E58" s="3">
         <v>452470000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>495274000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>472089000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>440428000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>369483000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>393328000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>391066000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>420895000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>238258000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>237843000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>237482000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>246843000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>224926000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>229253000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>243549000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>236733000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5509,187 +5642,193 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>210955000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>237369000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>233390000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>105470000</v>
+      </c>
+      <c r="E59" s="3">
         <v>92543000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>98316000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100345000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>114326000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>95530000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>102820000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>97818000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>104445000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>224073000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>224615000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>214522000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>219625000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200419000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>191572000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>184607000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>193563000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>181799000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>175960000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>175302000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>183029000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>182798000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>172286000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>168658000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>173681000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>165026000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2755923000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2696684000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2720761000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2671973000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2690866000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2571665000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2565686000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2548220000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2628052000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5765,145 +5904,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>295388000</v>
+      </c>
+      <c r="E61" s="3">
         <v>264977000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>304412000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>289511000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>286608000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>311986000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>296888000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>288111000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>284228000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>259610000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>267368000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>269623000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>270553000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>270983000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>276282000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>265883000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>235050000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>260968000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>255616000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>261530000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>253601000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>216602000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>236167000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>238011000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>233929000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>229392000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2532000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2666000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2608000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2620000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2777000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3155000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3452000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3548000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2181000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5979,8 +6124,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3053843000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2965960000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3027781000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2964104000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,22 +6824,25 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>20499000</v>
+      </c>
+      <c r="E70" s="3">
         <v>23159000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>24554000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>26548000</v>
-      </c>
-      <c r="G70" s="3">
-        <v>28397000</v>
       </c>
       <c r="H70" s="3">
         <v>28397000</v>
@@ -6693,31 +6860,31 @@
         <v>28397000</v>
       </c>
       <c r="M70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="N70" s="3">
         <v>29134000</v>
       </c>
       <c r="O70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="P70" s="3">
         <v>27137000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>23441000</v>
       </c>
       <c r="R70" s="3">
         <v>23441000</v>
       </c>
       <c r="S70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="T70" s="3">
         <v>24319000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="U70" s="3">
-        <v>23427000</v>
       </c>
       <c r="V70" s="3">
         <v>23427000</v>
@@ -6726,16 +6893,16 @@
         <v>23427000</v>
       </c>
       <c r="X70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>23401000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>23606000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>22326000</v>
       </c>
       <c r="AB70" s="3">
         <v>22326000</v>
@@ -6744,19 +6911,19 @@
         <v>22326000</v>
       </c>
       <c r="AD70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AE70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AG70" s="3">
         <v>22323000</v>
       </c>
       <c r="AH70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AI70" s="3">
         <v>25220000</v>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>25220000</v>
       </c>
+      <c r="AL70" s="3">
+        <v>25220000</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>247315000</v>
+      </c>
+      <c r="E72" s="3">
         <v>242349000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>237954000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>233597000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>228902000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>224672000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>223749000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>218397000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>213062000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>207003000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>201957000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>197159000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>192929000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>188064000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>183007000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>177499000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>170082000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>164088000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>160447000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>157578000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>155866000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>156319000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>151183000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>147577000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>141888000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>136314000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>275082000</v>
+      </c>
+      <c r="E76" s="3">
         <v>272400000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271958000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>267344000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>265155000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>263249000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>258667000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>254922000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>251799000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>244800000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>240390000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>239984000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>239480000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>245358000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>249023000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>253678000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>249681000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>248414000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>245423000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>242210000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>241491000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>241409000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>244781000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>246719000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>244684000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>242999000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7396000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6665000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6896000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6897000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6674000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3144000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7802000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7408000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8161000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6904000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6579000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5932000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6600000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6773000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7260000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8964000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7560000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5208000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4440000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3284000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3541000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6748000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5272000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7109000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6869000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7039000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E83" s="3">
         <v>508000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>497000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>491000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>483000</v>
       </c>
       <c r="H83" s="3">
         <v>483000</v>
       </c>
       <c r="I83" s="3">
+        <v>483000</v>
+      </c>
+      <c r="J83" s="3">
         <v>471000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>472000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>474000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>502000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>491000</v>
       </c>
       <c r="N83" s="3">
         <v>491000</v>
       </c>
       <c r="O83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="P83" s="3">
         <v>494000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>495000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>473000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>469000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>461000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>487000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>476000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>448000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>432000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>439000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>438000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>434000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>418000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>524000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>515000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>513000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>511000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>515000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>523000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>531000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>534000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>549000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2184000</v>
+      </c>
+      <c r="E89" s="3">
         <v>25914000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-37276000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18096000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32724000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11772000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11786000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30998000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13154000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44651000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9795000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>54594000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>19043000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>59103000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15101000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,8 +8781,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8591,8 +8811,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8669,8 +8889,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89010000</v>
+      </c>
+      <c r="E94" s="3">
         <v>9410000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27258000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1523000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>57884000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>30846000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14380000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>34761000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>16738000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>54977000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,8 +9261,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9058,86 +9291,89 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-464000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,325 +9699,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>72832000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-36768000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36779000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8300000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>68658000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11291000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>27628000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>126121000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40886000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>83040000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>43663000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>51320000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>113627000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>77938000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>129132000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>161147000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>22828000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>7923000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>30556000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1466000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1515000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-640000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>348000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4234000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4234000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-417000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-936000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>526000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>807000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1719000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1179000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-949000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>508000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1024000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-607000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>229000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>227000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>414000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>651000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>813000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16535000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5475000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25043000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7228000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>146015000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25227000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6974000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>68367000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19824000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>79457000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11660000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38956000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>88830000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4466000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-229000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,247 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24871000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25886000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23895000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23803000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23869000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24499000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22455000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23933000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24072000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25327000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25075000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19621000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14975000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12894000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12554000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12336000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11387000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11395000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11461000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11486000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12540000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16098000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16926000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17916000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18224000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18170000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17836000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1005,41 +1011,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>24871000</v>
+      </c>
+      <c r="E10" s="3">
         <v>25886000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23895000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23803000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23869000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24499000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22455000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23933000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24072000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25327000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,8 +1391,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1395,20 +1414,20 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>3700000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1485,41 +1504,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E15" s="3">
         <v>565000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>559000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>549000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>543000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>538000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>527000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>517000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>510000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>503000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1562,8 +1584,8 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>5</v>
@@ -1580,23 +1602,26 @@
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17183000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17770000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16787000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16479000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16309000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17237000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15631000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15838000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16038000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16238000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11486000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6754000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3054000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1352000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>655000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>618000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-467000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-662000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2061000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2329000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2809000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5129000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5727000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6508000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6892000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6808000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6237000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7688000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8116000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7108000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7324000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7560000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7262000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6824000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8095000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8034000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9089000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13589000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12867000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11921000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11542000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11899000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11718000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11854000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12057000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9400000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9157000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9731000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10969000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11199000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11408000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11332000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11362000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11599000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,8 +1924,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1924,196 +1957,202 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8259000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8681000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7667000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7873000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8103000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7800000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7351000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8612000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8544000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9592000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8399000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8792000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7383000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8373000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8313000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9423000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8511000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9627000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6606000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5022000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4247000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4963000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8608000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7297000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9393000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9185000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9222000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,8 +2183,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2222,228 +2261,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7688000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8116000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7108000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7324000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7560000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7262000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3124000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8095000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8034000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9089000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7897000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8301000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6892000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7879000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7818000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8950000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8042000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9166000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6119000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4546000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3799000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4531000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8169000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6859000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8959000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8767000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8698000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>572000</v>
+      </c>
+      <c r="E24" s="3">
         <v>720000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>443000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>428000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>663000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>588000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-20000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>293000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>626000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>928000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>765000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1219000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>645000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>812000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>805000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1259000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1116000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>649000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-335000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>266000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>521000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1175000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1082000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1611000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1456000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7116000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7396000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6665000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6896000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6897000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6674000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3144000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7802000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7408000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8161000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7132000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7082000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6247000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7067000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7013000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7691000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9224000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8050000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5470000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4881000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3533000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4010000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6994000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5777000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7348000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7311000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7278000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6825000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6990000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6399000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6380000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6582000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6142000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2838000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7270000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7102000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7656000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6904000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6579000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5932000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6600000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6773000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7260000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8964000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7560000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5208000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4440000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3284000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3541000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6748000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5272000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7109000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6869000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7039000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2956,8 +3016,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2974,12 +3034,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2992,8 +3052,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,8 +3278,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3244,196 +3313,202 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>5692000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4566000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5029000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3663000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4081000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2768000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3812000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2891000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3281000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4611000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5932000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6438000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3030000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4549000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2373000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2595000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2901000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7116000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7396000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6665000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6896000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6897000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6674000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3144000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7802000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7408000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8161000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6904000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6579000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5932000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6600000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6773000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7260000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8964000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7560000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5208000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4440000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3284000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3541000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6748000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5272000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7109000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6869000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7039000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7116000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7396000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6665000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6896000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6897000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6674000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3144000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7802000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7408000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8161000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6904000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6579000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5932000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6600000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6773000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7260000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8964000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7560000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5208000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4440000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3284000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3541000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6748000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5272000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7109000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6869000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7039000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,261 +3932,268 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>259011000</v>
+      </c>
+      <c r="E41" s="3">
         <v>267679000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>284014000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>288789000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>315232000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>308104000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>327473000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>345626000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>368053000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>369718000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>230203000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>204976000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>198002000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>273934000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>348221000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>279854000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>260030000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>326101000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>380463000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>301006000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>289346000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>250390000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>161560000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>157094000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171394000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>171623000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>177404000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>579132000</v>
+      </c>
+      <c r="E42" s="3">
         <v>538712000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>464861000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>538978000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>535606000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>522628000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>473632000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>515333000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>488346000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>523405000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>619583000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>648110000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>635345000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>669384000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>540288000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>597847000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>609181000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>589785000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>556637000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>631630000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>728899000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>565229000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>552015000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>587959000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>553668000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>557950000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>526698000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>89664000</v>
+      </c>
+      <c r="E43" s="3">
         <v>76029000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>77947000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>86867000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>76478000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>81606000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>77381000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>70047000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>69900000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>75902000</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4177,41 +4269,44 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E44" s="3">
         <v>118000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>145000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>60000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>218000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>90000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>145000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>93000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>97000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>117000</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -4287,41 +4382,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>184632000</v>
+      </c>
+      <c r="E45" s="3">
         <v>175555000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>174628000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>186396000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>156237000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>158924000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>135315000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>158984000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>156949000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>145314000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4397,41 +4495,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1124963000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1070860000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1017240000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1118241000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1096214000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1085223000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1025548000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1103774000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1095633000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1127765000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4507,41 +4608,44 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>932526000</v>
+      </c>
+      <c r="E47" s="3">
         <v>941479000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>919022000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>894896000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>880023000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>927922000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>872984000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>795516000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>773100000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>812954000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4617,118 +4721,124 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12254000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12151000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20695000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12033000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11917000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20889000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21005000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21008000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21036000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21235000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21265000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20860000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20979000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21040000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21066000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20775000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20777000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20476000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21000000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20802000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33690000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20892000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20261000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20293000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20326000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19851000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9906000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4757,10 +4867,10 @@
         <v>69021000</v>
       </c>
       <c r="L49" s="3">
+        <v>69021000</v>
+      </c>
+      <c r="M49" s="3">
         <v>69022000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>71122000</v>
       </c>
       <c r="N49" s="3">
         <v>71122000</v>
@@ -4772,31 +4882,31 @@
         <v>71122000</v>
       </c>
       <c r="Q49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="R49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>71223000</v>
       </c>
       <c r="S49" s="3">
         <v>71223000</v>
       </c>
       <c r="T49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="U49" s="3">
         <v>71051000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>70551000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>70551000</v>
       </c>
       <c r="X49" s="3">
         <v>70551000</v>
       </c>
       <c r="Y49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="Z49" s="3">
         <v>70651000</v>
@@ -4808,37 +4918,40 @@
         <v>70651000</v>
       </c>
       <c r="AC49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>72525000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,41 +5173,44 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>168613000</v>
+      </c>
+      <c r="E52" s="3">
         <v>158544000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>152946000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>167553000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>157274000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>134805000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>151203000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>127909000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>126134000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>129789000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5159,16 +5278,19 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AL52" s="3" t="s">
+      <c r="AM52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3441142000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3349424000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3261519000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3324293000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3257996000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,41 +5596,42 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2011613000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1989564000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1965467000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1930352000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1910491000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1946496000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1923827000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1884601000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1877209000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1910402000</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -5577,65 +5707,68 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>508428000</v>
+      </c>
+      <c r="E58" s="3">
         <v>478451000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>452470000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>495274000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>472089000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>440428000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>369483000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>393328000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>391066000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>420895000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>238258000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>237843000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>237482000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>246843000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>224926000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>229253000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>243549000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>236733000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5645,193 +5778,199 @@
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>210955000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>237369000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>233390000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>107426000</v>
+      </c>
+      <c r="E59" s="3">
         <v>105470000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92543000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98316000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100345000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>114326000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>95530000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>102820000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>97818000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>104445000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>224073000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>224615000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>214522000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>219625000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200419000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>191572000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>184607000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>193563000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>181799000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>175960000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>175302000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>183029000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>182798000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>172286000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>168658000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>173681000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>165026000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2829216000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2755923000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2696684000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2720761000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2671973000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2690866000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2571665000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2565686000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2548220000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2628052000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5907,151 +6046,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>310844000</v>
+      </c>
+      <c r="E61" s="3">
         <v>295388000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>264977000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>304412000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>289511000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>286608000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>311986000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>296888000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>288111000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>284228000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>259610000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>267368000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>269623000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>270553000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>270983000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>276282000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>265883000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>235050000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>260968000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>255616000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>261530000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>253601000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>216602000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>236167000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>238011000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>233929000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>229392000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1483000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2532000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2666000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2608000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2620000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2777000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3155000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3452000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3548000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2181000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6127,8 +6272,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3141543000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3053843000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2965960000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3027781000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2964104000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,25 +6991,28 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>23495000</v>
+      </c>
+      <c r="E70" s="3">
         <v>20499000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>23159000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>24554000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>26548000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>28397000</v>
       </c>
       <c r="I70" s="3">
         <v>28397000</v>
@@ -6863,31 +7030,31 @@
         <v>28397000</v>
       </c>
       <c r="N70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="O70" s="3">
         <v>29134000</v>
       </c>
       <c r="P70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="Q70" s="3">
         <v>27137000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="R70" s="3">
-        <v>23441000</v>
       </c>
       <c r="S70" s="3">
         <v>23441000</v>
       </c>
       <c r="T70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="U70" s="3">
         <v>24319000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="V70" s="3">
-        <v>23427000</v>
       </c>
       <c r="W70" s="3">
         <v>23427000</v>
@@ -6896,16 +7063,16 @@
         <v>23427000</v>
       </c>
       <c r="Y70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="Z70" s="3">
         <v>23401000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>23606000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>22326000</v>
       </c>
       <c r="AC70" s="3">
         <v>22326000</v>
@@ -6914,19 +7081,19 @@
         <v>22326000</v>
       </c>
       <c r="AE70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AF70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AG70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AH70" s="3">
         <v>22323000</v>
       </c>
       <c r="AI70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AJ70" s="3">
         <v>25220000</v>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>25220000</v>
       </c>
+      <c r="AM70" s="3">
+        <v>25220000</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>252180000</v>
+      </c>
+      <c r="E72" s="3">
         <v>247315000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>242349000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>237954000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>233597000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>228902000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>224672000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>223749000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>218397000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>213062000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>207003000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>201957000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>197159000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>192929000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>188064000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>183007000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>177499000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>170082000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>164088000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>160447000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>157578000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>155866000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>156319000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>151183000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>147577000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>141888000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>136314000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>276104000</v>
+      </c>
+      <c r="E76" s="3">
         <v>275082000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>272400000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>271958000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>267344000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>265155000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>263249000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>258667000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>254922000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>251799000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>244800000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>240390000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>239984000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>239480000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>245358000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>249023000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>253678000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>249681000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>248414000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>245423000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>242210000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>241491000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>241409000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>244781000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>246719000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>244684000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>242999000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7116000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7396000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6665000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6896000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6897000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6674000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3144000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7802000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7408000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8161000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6904000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6579000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5932000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6600000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6773000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7260000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8964000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7560000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5208000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4440000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3284000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3541000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6748000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5272000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7109000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6869000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7039000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,118 +8169,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E83" s="3">
         <v>518000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>508000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>497000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>491000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>483000</v>
       </c>
       <c r="I83" s="3">
         <v>483000</v>
       </c>
       <c r="J83" s="3">
+        <v>483000</v>
+      </c>
+      <c r="K83" s="3">
         <v>471000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>472000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>474000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>502000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>491000</v>
       </c>
       <c r="O83" s="3">
         <v>491000</v>
       </c>
       <c r="P83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>494000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>495000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>473000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>469000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>461000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>487000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>476000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>448000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>432000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>439000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>438000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>434000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>418000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>524000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>515000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>513000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>511000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>515000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>523000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>531000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>534000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>549000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9132000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2184000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25914000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37276000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18096000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32724000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11772000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11786000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>30998000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13154000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>44651000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9795000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>54594000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>19043000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>59103000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15101000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,8 +9001,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8814,8 +9034,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8892,8 +9112,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56918000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89010000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9410000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27258000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1523000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>57884000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>30846000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14380000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>34761000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>16738000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>54977000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,8 +9494,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9294,86 +9527,89 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-464000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,334 +9944,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>55059000</v>
+      </c>
+      <c r="E100" s="3">
         <v>72832000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36768000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36779000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8300000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>68658000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11291000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>27628000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>126121000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>40886000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>83040000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>43663000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>51320000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>113627000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>77938000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>129132000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>161147000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>22828000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7923000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>30556000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1045000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1466000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1515000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-640000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>348000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4234000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4234000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-417000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-936000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>526000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>807000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1719000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1179000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-949000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>508000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1024000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-607000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>229000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>227000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>414000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>651000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>813000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7568000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16535000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5475000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-25043000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7228000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>146015000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25227000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6974000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>68367000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19824000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>79457000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11660000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38956000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>88830000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4466000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-229000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29872000</v>
+      </c>
+      <c r="E8" s="3">
         <v>26793000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24871000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25886000</v>
       </c>
-      <c r="G8" s="3">
-        <v>23895000</v>
-      </c>
       <c r="H8" s="3">
+        <v>27864000</v>
+      </c>
+      <c r="I8" s="3">
         <v>23803000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23869000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24499000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22455000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23933000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24072000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25327000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25075000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19621000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14975000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12894000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12554000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12336000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11387000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11395000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11461000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11486000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12540000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16098000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16926000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17916000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>18224000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18170000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17836000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1023,47 +1029,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29872000</v>
+      </c>
+      <c r="E10" s="3">
         <v>26793000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24871000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25886000</v>
       </c>
-      <c r="G10" s="3">
-        <v>23895000</v>
-      </c>
       <c r="H10" s="3">
+        <v>27864000</v>
+      </c>
+      <c r="I10" s="3">
         <v>23803000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23869000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24499000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22455000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23933000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24072000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25327000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1139,8 +1148,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,8 +1429,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1439,20 +1458,20 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>3700000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1529,47 +1548,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>594000</v>
+      </c>
+      <c r="E15" s="3">
         <v>584000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>571000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>565000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>559000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>549000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>543000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>538000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>527000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>517000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>510000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>503000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1612,8 +1634,8 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
@@ -1630,23 +1652,26 @@
       <c r="AI15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17437000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17337000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17183000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17770000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16787000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16479000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16309000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17237000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15631000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15838000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16038000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16238000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11486000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6754000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3054000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1352000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>655000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>618000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-467000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-662000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2061000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2329000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2809000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5129000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5727000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6508000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6892000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6808000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6237000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12435000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9456000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7688000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8116000</v>
       </c>
-      <c r="G18" s="3">
-        <v>7108000</v>
-      </c>
       <c r="H18" s="3">
+        <v>11077000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7324000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7560000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7262000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6824000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8095000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8034000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9089000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13589000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12867000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11921000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11542000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11899000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11718000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11854000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12057000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9400000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9157000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9731000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10969000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11199000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11408000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11332000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11362000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11599000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,202 +2029,208 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13029000</v>
+      </c>
+      <c r="E21" s="3">
         <v>10040000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8259000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8681000</v>
       </c>
-      <c r="G21" s="3">
-        <v>7667000</v>
-      </c>
       <c r="H21" s="3">
+        <v>11636000</v>
+      </c>
+      <c r="I21" s="3">
         <v>7873000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8103000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7800000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7351000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8612000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8544000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9592000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8399000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8792000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7383000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8373000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8313000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9423000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8511000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9627000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6606000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5022000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4247000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4963000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8608000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7297000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9393000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9185000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9222000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2228,8 +2267,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2306,240 +2345,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12435000</v>
+      </c>
+      <c r="E23" s="3">
         <v>9456000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7688000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8116000</v>
       </c>
-      <c r="G23" s="3">
-        <v>7108000</v>
-      </c>
       <c r="H23" s="3">
+        <v>11077000</v>
+      </c>
+      <c r="I23" s="3">
         <v>7324000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7560000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7262000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3124000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8095000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8034000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9089000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7897000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8301000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6892000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7879000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7818000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8950000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8042000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9166000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6119000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4546000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3799000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4531000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8169000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6859000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8959000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8767000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8698000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4907000</v>
+      </c>
+      <c r="E24" s="3">
         <v>987000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>572000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>720000</v>
       </c>
-      <c r="G24" s="3">
-        <v>443000</v>
-      </c>
       <c r="H24" s="3">
+        <v>4571000</v>
+      </c>
+      <c r="I24" s="3">
         <v>428000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>663000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>588000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-20000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>293000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>626000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>928000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>765000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1219000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>645000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>812000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>805000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1259000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1116000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>649000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-335000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>266000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>521000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1175000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1082000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1611000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1456000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7528000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8469000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7116000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7396000</v>
       </c>
-      <c r="G26" s="3">
-        <v>6665000</v>
-      </c>
       <c r="H26" s="3">
+        <v>6506000</v>
+      </c>
+      <c r="I26" s="3">
         <v>6896000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6897000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6674000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3144000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7802000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7408000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8161000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7132000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7082000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6247000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7067000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7013000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7691000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9224000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8050000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5470000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4881000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3533000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4010000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6994000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5777000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7348000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7311000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7278000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7200000</v>
+      </c>
+      <c r="E27" s="3">
         <v>8040000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6825000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6990000</v>
       </c>
-      <c r="G27" s="3">
-        <v>6399000</v>
-      </c>
       <c r="H27" s="3">
+        <v>6240000</v>
+      </c>
+      <c r="I27" s="3">
         <v>6380000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6582000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6142000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2838000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7270000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7102000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7656000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6904000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6579000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5932000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6600000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6773000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7260000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8964000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7560000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5208000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4440000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3284000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3541000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6748000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5272000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7109000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6869000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7039000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3082,8 +3142,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -3100,12 +3160,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,202 +3457,208 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>5692000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4566000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5029000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3663000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4081000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2768000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3812000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2891000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3281000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4611000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5932000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6438000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3030000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4549000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2373000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2595000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2901000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7528000</v>
+      </c>
+      <c r="E33" s="3">
         <v>8469000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7116000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7396000</v>
       </c>
-      <c r="G33" s="3">
-        <v>6665000</v>
-      </c>
       <c r="H33" s="3">
+        <v>6506000</v>
+      </c>
+      <c r="I33" s="3">
         <v>6896000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6897000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6674000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3144000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7802000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7408000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8161000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6904000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6579000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5932000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6600000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6773000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7260000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8964000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7560000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5208000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4440000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3284000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3541000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6748000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5272000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7109000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6869000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7039000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7528000</v>
+      </c>
+      <c r="E35" s="3">
         <v>8469000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7116000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7396000</v>
       </c>
-      <c r="G35" s="3">
-        <v>6665000</v>
-      </c>
       <c r="H35" s="3">
+        <v>6506000</v>
+      </c>
+      <c r="I35" s="3">
         <v>6896000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6897000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6674000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3144000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7802000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7408000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8161000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6904000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6579000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5932000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6600000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6773000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7260000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8964000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7560000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5208000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4440000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3284000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3541000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6748000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5272000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7109000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6869000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7039000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,279 +4104,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>225345000</v>
+      </c>
+      <c r="E41" s="3">
         <v>239607000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>259011000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>267679000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>284014000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>288789000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>315232000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>308104000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>327473000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>345626000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>368053000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>369718000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>230203000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>204976000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>198002000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>273934000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>348221000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>279854000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>260030000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>326101000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>380463000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>301006000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>289346000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>250390000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>161560000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>157094000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>171394000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171623000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>177404000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>544818000</v>
+      </c>
+      <c r="E42" s="3">
         <v>535510000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>579132000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>538712000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>464861000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>538978000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>535606000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>522628000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>473632000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>515333000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>488346000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>523405000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>619583000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>648110000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>635345000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>669384000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>540288000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>597847000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>609181000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>589785000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>556637000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>631630000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>728899000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>565229000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>552015000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>587959000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>553668000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>557950000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>526698000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>93986000</v>
+      </c>
+      <c r="E43" s="3">
         <v>95563000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>89664000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>76029000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>77947000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>86867000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>76478000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>81606000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>77381000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>70047000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>69900000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>75902000</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4367,47 +4459,50 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>123000</v>
+        <v>101000</v>
       </c>
       <c r="E44" s="3">
         <v>123000</v>
       </c>
       <c r="F44" s="3">
+        <v>123000</v>
+      </c>
+      <c r="G44" s="3">
         <v>118000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>145000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>60000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>218000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>90000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>145000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>93000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>97000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>117000</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -4483,47 +4578,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>190069000</v>
+      </c>
+      <c r="E45" s="3">
         <v>179083000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>184632000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>175555000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>174628000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>186396000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>156237000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>158924000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>135315000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>158984000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>156949000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>145314000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4599,47 +4697,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1065984000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1063617000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1124963000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1070860000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1017240000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1118241000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1096214000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1085223000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1025548000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1103774000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1095633000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1127765000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,47 +4816,50 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>927314000</v>
+      </c>
+      <c r="E47" s="3">
         <v>938180000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>932526000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>941479000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>919022000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>894896000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>880023000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>927922000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>872984000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>795516000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>773100000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>812954000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4831,124 +4935,130 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20911000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12348000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12254000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12151000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20695000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12033000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11917000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20889000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21005000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21008000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21036000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21235000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21265000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20860000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20979000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21040000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21066000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20775000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20777000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20476000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21000000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20802000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33690000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20892000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20261000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20293000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20326000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19851000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9906000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4983,10 +5093,10 @@
         <v>69021000</v>
       </c>
       <c r="N49" s="3">
+        <v>69021000</v>
+      </c>
+      <c r="O49" s="3">
         <v>69022000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>71122000</v>
       </c>
       <c r="P49" s="3">
         <v>71122000</v>
@@ -4998,31 +5108,31 @@
         <v>71122000</v>
       </c>
       <c r="S49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="T49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>71223000</v>
       </c>
       <c r="U49" s="3">
         <v>71223000</v>
       </c>
       <c r="V49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="W49" s="3">
         <v>71051000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>70551000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>70551000</v>
       </c>
       <c r="Z49" s="3">
         <v>70551000</v>
       </c>
       <c r="AA49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="AB49" s="3">
         <v>70651000</v>
@@ -5034,37 +5144,40 @@
         <v>70651000</v>
       </c>
       <c r="AE49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>72525000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,47 +5411,50 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>156011000</v>
+      </c>
+      <c r="E52" s="3">
         <v>167902000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>168613000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>158544000</v>
       </c>
-      <c r="G52" s="3">
-        <v>152946000</v>
-      </c>
       <c r="H52" s="3">
+        <v>152726000</v>
+      </c>
+      <c r="I52" s="3">
         <v>167553000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>157274000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>134805000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>151203000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>127909000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>126134000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>129789000</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -5403,16 +5522,19 @@
         <v>0</v>
       </c>
       <c r="AL52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3411738000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3403716000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3441142000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3349424000</v>
       </c>
-      <c r="G54" s="3">
-        <v>3261519000</v>
-      </c>
       <c r="H54" s="3">
+        <v>3261299000</v>
+      </c>
+      <c r="I54" s="3">
         <v>3324293000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3257996000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,47 +5856,48 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2018729000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2002208000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2011613000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1989564000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1965467000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1930352000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1910491000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1946496000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1923827000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1884601000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1877209000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1910402000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5843,71 +5973,74 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>483622000</v>
+      </c>
+      <c r="E58" s="3">
         <v>446906000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>508428000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>478451000</v>
       </c>
-      <c r="G58" s="3">
-        <v>452470000</v>
-      </c>
       <c r="H58" s="3">
+        <v>425033000</v>
+      </c>
+      <c r="I58" s="3">
         <v>495274000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>472089000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>440428000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>369483000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>393328000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>391066000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>420895000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>238258000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>237843000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>237482000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>246843000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>224926000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>229253000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>243549000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>236733000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5917,205 +6050,211 @@
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>210955000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>237369000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>233390000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>105996000</v>
+      </c>
+      <c r="E59" s="3">
         <v>117322000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>107426000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>105470000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>92543000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>98316000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100345000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>114326000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>95530000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>102820000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97818000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>104445000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>224073000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>224615000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>214522000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>219625000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200419000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>191572000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>184607000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>193563000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>181799000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>175960000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>175302000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>183029000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>182798000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>172286000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>168658000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>173681000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>165026000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2820718000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2779947000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2829216000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2755923000</v>
       </c>
-      <c r="G60" s="3">
-        <v>2696684000</v>
-      </c>
       <c r="H60" s="3">
+        <v>2670625000</v>
+      </c>
+      <c r="I60" s="3">
         <v>2720761000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2671973000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2690866000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2571665000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2565686000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2548220000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2628052000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,163 +6330,169 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>283450000</v>
+      </c>
+      <c r="E61" s="3">
         <v>317076000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>310844000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>295388000</v>
       </c>
-      <c r="G61" s="3">
-        <v>264977000</v>
-      </c>
       <c r="H61" s="3">
+        <v>292414000</v>
+      </c>
+      <c r="I61" s="3">
         <v>304412000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>289511000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>286608000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>311986000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>296888000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>288111000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>284228000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>259610000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>267368000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>269623000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>270553000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>270983000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>276282000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>265883000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>235050000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>260968000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>255616000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>261530000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>253601000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>216602000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>236167000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>238011000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>233929000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>229392000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2672000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2541000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1483000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2532000</v>
       </c>
-      <c r="G62" s="3">
-        <v>2666000</v>
-      </c>
       <c r="H62" s="3">
+        <v>2664000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2608000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2620000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2777000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3155000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3452000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3548000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2181000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6423,8 +6568,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3108495000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3099564000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3141543000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3053843000</v>
       </c>
-      <c r="G66" s="3">
-        <v>2965960000</v>
-      </c>
       <c r="H66" s="3">
+        <v>2967336000</v>
+      </c>
+      <c r="I66" s="3">
         <v>3027781000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2964104000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7170,22 +7337,22 @@
         <v>25992000</v>
       </c>
       <c r="E70" s="3">
+        <v>25992000</v>
+      </c>
+      <c r="F70" s="3">
         <v>23495000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>20499000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>23159000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>24554000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>26548000</v>
-      </c>
-      <c r="J70" s="3">
-        <v>28397000</v>
       </c>
       <c r="K70" s="3">
         <v>28397000</v>
@@ -7203,31 +7370,31 @@
         <v>28397000</v>
       </c>
       <c r="P70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="Q70" s="3">
         <v>29134000</v>
       </c>
       <c r="R70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="S70" s="3">
         <v>27137000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="T70" s="3">
-        <v>23441000</v>
       </c>
       <c r="U70" s="3">
         <v>23441000</v>
       </c>
       <c r="V70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="W70" s="3">
         <v>24319000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="X70" s="3">
-        <v>23427000</v>
       </c>
       <c r="Y70" s="3">
         <v>23427000</v>
@@ -7236,16 +7403,16 @@
         <v>23427000</v>
       </c>
       <c r="AA70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="AB70" s="3">
         <v>23401000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>23606000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>22326000</v>
       </c>
       <c r="AE70" s="3">
         <v>22326000</v>
@@ -7254,19 +7421,19 @@
         <v>22326000</v>
       </c>
       <c r="AG70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AH70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AJ70" s="3">
         <v>22323000</v>
       </c>
       <c r="AK70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AL70" s="3">
         <v>25220000</v>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>25220000</v>
       </c>
+      <c r="AO70" s="3">
+        <v>25220000</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>261693000</v>
+      </c>
+      <c r="E72" s="3">
         <v>258141000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>252180000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>247315000</v>
       </c>
-      <c r="G72" s="3">
-        <v>242349000</v>
-      </c>
       <c r="H72" s="3">
+        <v>240753000</v>
+      </c>
+      <c r="I72" s="3">
         <v>237954000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>233597000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>228902000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>224672000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>223749000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>218397000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>213062000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>207003000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>201957000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>197159000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>192929000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>188064000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>183007000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>177499000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>170082000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>164088000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>160447000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>157578000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>155866000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>156319000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>151183000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>147577000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>141888000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>136314000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>277251000</v>
+      </c>
+      <c r="E76" s="3">
         <v>278160000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>276104000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>275082000</v>
       </c>
-      <c r="G76" s="3">
-        <v>272400000</v>
-      </c>
       <c r="H76" s="3">
+        <v>270804000</v>
+      </c>
+      <c r="I76" s="3">
         <v>271958000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>267344000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>265155000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>263249000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>258667000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>254922000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>251799000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>244800000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>240390000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>239984000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>239480000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>245358000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>249023000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>253678000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>249681000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>248414000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>245423000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>242210000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>241491000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>241409000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>244781000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>246719000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>244684000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>242999000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7528000</v>
+      </c>
+      <c r="E81" s="3">
         <v>8469000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7116000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7396000</v>
       </c>
-      <c r="G81" s="3">
-        <v>6665000</v>
-      </c>
       <c r="H81" s="3">
+        <v>6506000</v>
+      </c>
+      <c r="I81" s="3">
         <v>6896000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6897000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6674000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3144000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7802000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7408000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8161000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6904000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6579000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5932000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6600000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6773000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7260000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8964000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7560000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5208000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4440000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3284000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3541000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6748000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5272000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7109000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6869000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7039000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E83" s="3">
         <v>529000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>524000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>518000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>508000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>497000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>491000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>483000</v>
       </c>
       <c r="K83" s="3">
         <v>483000</v>
       </c>
       <c r="L83" s="3">
+        <v>483000</v>
+      </c>
+      <c r="M83" s="3">
         <v>471000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>472000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>474000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>502000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>491000</v>
       </c>
       <c r="Q83" s="3">
         <v>491000</v>
       </c>
       <c r="R83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="S83" s="3">
         <v>494000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>495000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>473000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>469000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>461000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>487000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>476000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>448000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>432000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>439000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>438000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>434000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>418000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>524000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>515000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>513000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>511000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>515000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>523000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>531000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>534000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>549000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22945000</v>
+      </c>
+      <c r="E89" s="3">
         <v>46874000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9132000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2184000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25914000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37276000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18096000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32724000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11772000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11786000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30998000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13154000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>44651000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9795000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>54594000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>19043000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>59103000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15101000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,8 +9441,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9260,8 +9480,8 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -9338,8 +9558,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1172000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1943000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-56918000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-89010000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>9410000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27258000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1523000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>57884000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>30846000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14380000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>34761000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>16738000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>54977000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,8 +9960,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9766,86 +9999,89 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-464000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,352 +10434,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10047000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-67990000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>55059000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>72832000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-36768000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36779000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8300000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>68658000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>11291000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>27628000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>126121000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>40886000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>83040000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>43663000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>51320000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>113627000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>77938000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>129132000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>161147000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>22828000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>7923000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>30556000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4031000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2712000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1045000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1466000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1515000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-640000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>348000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4234000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4234000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-417000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-936000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>526000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>807000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1719000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1179000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-949000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>508000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1024000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-607000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>229000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>700000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>414000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>651000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>813000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14662000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19504000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7568000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16535000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5475000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25043000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7228000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>146015000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25227000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6974000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>68367000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19824000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>79457000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11660000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38956000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>88830000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4466000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-229000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-27773000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>BAC</t>
   </si>
@@ -656,265 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28935000</v>
+      </c>
+      <c r="E8" s="3">
         <v>29872000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26793000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24871000</v>
       </c>
-      <c r="G8" s="3">
-        <v>25886000</v>
-      </c>
       <c r="H8" s="3">
+        <v>26767000</v>
+      </c>
+      <c r="I8" s="3">
         <v>27864000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23803000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23869000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24499000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22455000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23933000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24072000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25327000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>25075000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19621000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14975000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12894000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12554000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12336000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11387000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11395000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11461000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11486000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12540000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16098000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16926000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17916000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18224000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>18170000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17836000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16965000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16369000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>15599000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>15066000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>14657000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>14146000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>13710000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12865000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>12610000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1032,50 +1038,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28935000</v>
+      </c>
+      <c r="E10" s="3">
         <v>29872000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26793000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24871000</v>
       </c>
-      <c r="G10" s="3">
-        <v>25886000</v>
-      </c>
       <c r="H10" s="3">
+        <v>26767000</v>
+      </c>
+      <c r="I10" s="3">
         <v>27864000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23803000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23869000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24499000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22455000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23933000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24072000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25327000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1151,8 +1160,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1448,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1461,20 +1480,20 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>3700000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1551,50 +1570,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>605000</v>
+      </c>
+      <c r="E15" s="3">
         <v>594000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>584000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>571000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>565000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>559000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>549000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>543000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>538000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>527000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>517000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>510000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>503000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1637,8 +1659,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>5</v>
@@ -1655,23 +1677,26 @@
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-151000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-160000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-162000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-176000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-181000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18531000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17437000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17337000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17183000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17770000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16787000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16479000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16309000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17237000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15631000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15838000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16038000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16238000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11486000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6754000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3054000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1352000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>655000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>618000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-467000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-662000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2061000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2329000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2809000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5129000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5727000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6508000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6892000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6808000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6237000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5620000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5368000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4664000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4605000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4330000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3886000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3487000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3347000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3259000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10404000</v>
+      </c>
+      <c r="E18" s="3">
         <v>12435000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9456000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7688000</v>
       </c>
-      <c r="G18" s="3">
-        <v>8116000</v>
-      </c>
       <c r="H18" s="3">
+        <v>8997000</v>
+      </c>
+      <c r="I18" s="3">
         <v>11077000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7324000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7560000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7262000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6824000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8095000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8034000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9089000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13589000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12867000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11921000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11542000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11899000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11718000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11854000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12057000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9400000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9157000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9731000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10969000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11199000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11408000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11332000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11362000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11599000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11345000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>11001000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10935000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10461000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>10327000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>10260000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>10223000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>9518000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>9351000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2023,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,205 +2065,211 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-5692000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4566000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5029000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3663000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4081000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2768000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3812000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2891000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3281000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4611000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5932000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6438000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3030000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4549000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2595000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2901000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2351000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2503000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2541000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4056000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2716000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2139000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2903000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3595000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2047000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11009000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13029000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10040000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8259000</v>
       </c>
-      <c r="G21" s="3">
-        <v>8681000</v>
-      </c>
       <c r="H21" s="3">
+        <v>9562000</v>
+      </c>
+      <c r="I21" s="3">
         <v>11636000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7873000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8103000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7800000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7351000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8612000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8544000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9592000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8399000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8792000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7383000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8373000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8313000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9423000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8511000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9627000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6606000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5022000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4247000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4963000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8608000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7297000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9393000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9185000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9222000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9509000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9011000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8905000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6920000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>8134000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>8652000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>7854000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>6472000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>7868000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2270,8 +2309,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2348,246 +2387,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10404000</v>
+      </c>
+      <c r="E23" s="3">
         <v>12435000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9456000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7688000</v>
       </c>
-      <c r="G23" s="3">
-        <v>8116000</v>
-      </c>
       <c r="H23" s="3">
+        <v>8997000</v>
+      </c>
+      <c r="I23" s="3">
         <v>11077000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7324000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7560000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7262000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3124000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8095000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8034000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9089000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7897000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8301000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6892000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7879000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7818000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8950000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8042000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9166000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6119000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4546000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3799000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4531000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8169000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6859000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8959000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8767000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8698000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8994000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8498000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>8394000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6405000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7611000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>8121000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>7320000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5923000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>7304000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1820000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4907000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>987000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>572000</v>
       </c>
-      <c r="G24" s="3">
-        <v>720000</v>
-      </c>
       <c r="H24" s="3">
+        <v>1637000</v>
+      </c>
+      <c r="I24" s="3">
         <v>4571000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>428000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>663000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>588000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-20000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>293000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>626000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>928000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>765000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1219000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>645000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>812000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>805000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1259000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1182000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1116000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>649000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-335000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>266000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>521000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1175000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1082000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1611000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1456000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1827000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1714000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1476000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1932000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2187000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3015000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1983000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1311000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>2349000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8584000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7528000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8469000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7116000</v>
       </c>
-      <c r="G26" s="3">
-        <v>7396000</v>
-      </c>
       <c r="H26" s="3">
+        <v>7360000</v>
+      </c>
+      <c r="I26" s="3">
         <v>6506000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6896000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6897000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6674000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3144000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7802000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7408000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8161000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7132000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7082000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6247000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7067000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7013000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7691000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9224000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8050000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5470000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4881000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3533000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4010000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6994000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5777000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7348000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7311000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7278000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7167000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6784000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>6918000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4473000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5424000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5106000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4612000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>4955000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8155000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7200000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8040000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6825000</v>
       </c>
-      <c r="G27" s="3">
-        <v>6990000</v>
-      </c>
       <c r="H27" s="3">
+        <v>6954000</v>
+      </c>
+      <c r="I27" s="3">
         <v>6240000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6380000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6582000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6142000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2838000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7270000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7102000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7656000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6904000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6579000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5932000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6600000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6773000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7260000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8964000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7560000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5208000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4440000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3284000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3541000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6748000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5272000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7109000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6869000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7039000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6701000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6466000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>6490000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4187000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4959000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4745000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4835000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4251000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3163,12 +3223,12 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-1953000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3485,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,205 +3529,211 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>5692000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4566000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5029000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3663000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4081000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2768000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3812000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2891000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3281000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4611000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5932000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6438000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3030000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4549000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2373000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2595000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2901000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2351000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2503000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2541000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4056000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2716000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2139000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2903000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3595000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2047000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8584000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7528000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8469000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7116000</v>
       </c>
-      <c r="G33" s="3">
-        <v>7396000</v>
-      </c>
       <c r="H33" s="3">
+        <v>7360000</v>
+      </c>
+      <c r="I33" s="3">
         <v>6506000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6896000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6897000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6674000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3144000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7802000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7408000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8161000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6904000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6579000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5932000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6600000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6773000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7260000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8964000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7560000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5208000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4440000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3284000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3541000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6748000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5272000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7109000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6869000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7039000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6701000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6466000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>6490000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2234000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4959000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4745000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4835000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4251000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8584000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7528000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8469000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7116000</v>
       </c>
-      <c r="G35" s="3">
-        <v>7396000</v>
-      </c>
       <c r="H35" s="3">
+        <v>7360000</v>
+      </c>
+      <c r="I35" s="3">
         <v>6506000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6896000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6897000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6674000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3144000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7802000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7408000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8161000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6904000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6579000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5932000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6600000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6773000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7260000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8964000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7560000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5208000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4440000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3284000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3541000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6748000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5272000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7109000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6869000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7039000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6701000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6466000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>6490000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2234000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4959000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4745000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4835000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4251000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,288 +4190,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>235379000</v>
+      </c>
+      <c r="E41" s="3">
         <v>225345000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>239607000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>259011000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>267679000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>284014000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>288789000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>315232000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>308104000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>327473000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>345626000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>368053000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>369718000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>230203000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>204976000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>198002000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>273934000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>348221000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>279854000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>260030000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>326101000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>380463000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>301006000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>289346000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>250390000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>161560000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>157094000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171394000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171623000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>177404000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>184858000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>171199000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>204241000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>157434000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>172381000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>158704000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>168025000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>147738000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>143434000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>615906000</v>
+      </c>
+      <c r="E42" s="3">
         <v>544818000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>535510000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>579132000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>538712000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>464861000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>538978000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>535606000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>522628000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>473632000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>515333000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>488346000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>523405000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>619583000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>648110000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>635345000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>669384000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>540288000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>597847000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>609181000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>589785000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>556637000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>631630000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>728899000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>565229000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>552015000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>587959000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>553668000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>557950000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>526698000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>520837000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>483328000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>499045000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>471020000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>475410000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>482912000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>471822000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>430806000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>463061000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>91982000</v>
+      </c>
+      <c r="E43" s="3">
         <v>93986000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>95563000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>89664000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>76029000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>77947000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>86867000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>76478000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>81606000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>77381000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>70047000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69900000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>75902000</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4462,50 +4554,53 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E44" s="3">
         <v>101000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>123000</v>
       </c>
       <c r="F44" s="3">
         <v>123000</v>
       </c>
       <c r="G44" s="3">
-        <v>118000</v>
+        <v>123000</v>
       </c>
       <c r="H44" s="3">
+        <v>217000</v>
+      </c>
+      <c r="I44" s="3">
         <v>145000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>60000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>218000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>90000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>145000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>93000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>97000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>117000</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -4581,50 +4676,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>190080000</v>
+      </c>
+      <c r="E45" s="3">
         <v>190069000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>179083000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>184632000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>175555000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>174628000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>186396000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>156237000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>158924000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>135315000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>158984000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>156949000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>145314000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4700,50 +4798,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1151599000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1065984000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1063617000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1124963000</v>
       </c>
-      <c r="G46" s="3">
-        <v>1070860000</v>
-      </c>
       <c r="H46" s="3">
+        <v>1070959000</v>
+      </c>
+      <c r="I46" s="3">
         <v>1017240000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1118241000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1096214000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1085223000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1025548000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1103774000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1095633000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1127765000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4819,50 +4920,53 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>903200000</v>
+      </c>
+      <c r="E47" s="3">
         <v>927314000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>938180000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>932526000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>941479000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>919022000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>894896000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>880023000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>927922000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>872984000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>795516000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>773100000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>812954000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4938,127 +5042,133 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12539000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20911000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12348000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12254000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12151000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20695000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12033000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11917000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20889000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21005000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21008000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21036000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21235000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21265000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20860000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20979000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21040000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21066000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20775000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20777000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20476000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21000000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20802000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33690000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20892000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20261000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20293000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20326000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19851000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9906000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9680000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9537000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9399000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9247000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8971000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8904000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>9319000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>9139000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>9133000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5096,10 +5206,10 @@
         <v>69021000</v>
       </c>
       <c r="O49" s="3">
+        <v>69021000</v>
+      </c>
+      <c r="P49" s="3">
         <v>69022000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>71122000</v>
       </c>
       <c r="Q49" s="3">
         <v>71122000</v>
@@ -5111,31 +5221,31 @@
         <v>71122000</v>
       </c>
       <c r="T49" s="3">
+        <v>71122000</v>
+      </c>
+      <c r="U49" s="3">
         <v>71222000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>71223000</v>
       </c>
       <c r="V49" s="3">
         <v>71223000</v>
       </c>
       <c r="W49" s="3">
+        <v>71223000</v>
+      </c>
+      <c r="X49" s="3">
         <v>71051000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>70551000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>71151000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>70551000</v>
       </c>
       <c r="AA49" s="3">
         <v>70551000</v>
       </c>
       <c r="AB49" s="3">
-        <v>70651000</v>
+        <v>70551000</v>
       </c>
       <c r="AC49" s="3">
         <v>70651000</v>
@@ -5147,37 +5257,40 @@
         <v>70651000</v>
       </c>
       <c r="AF49" s="3">
+        <v>70651000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>72525000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>70859000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>70993000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>71128000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>73565000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>73834000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>74080000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>74345000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>74638000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>75389000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,50 +5530,53 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>167940000</v>
+      </c>
+      <c r="E52" s="3">
         <v>156011000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>167902000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>168613000</v>
       </c>
-      <c r="G52" s="3">
-        <v>158544000</v>
-      </c>
       <c r="H52" s="3">
+        <v>158445000</v>
+      </c>
+      <c r="I52" s="3">
         <v>152726000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>167553000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>157274000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>134805000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>151203000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>127909000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>126134000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>129789000</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5525,16 +5644,19 @@
         <v>0</v>
       </c>
       <c r="AM52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="3">
         <v>11025000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>10670000</v>
       </c>
-      <c r="AO52" s="3" t="s">
+      <c r="AP52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3496186000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3411738000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3403716000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3441142000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3349424000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3261299000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3324293000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3257996000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3273803000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3180151000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3153090000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3123198000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3194657000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3051375000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3072953000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3111606000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3238223000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3169495000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3085446000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3029894000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2969992000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2819627000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2738452000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2741688000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2619954000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2434079000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2426330000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2395892000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2377164000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2354507000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2338833000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2291670000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2328478000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2281234000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2283896000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2254529000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2247701000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2188067000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2195314000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,50 +5986,51 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2037663000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2018729000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2002208000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2011613000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1989564000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1965467000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1930352000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1910491000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1946496000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1923827000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1884601000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1877209000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1910402000</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -5976,74 +6106,77 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>493066000</v>
+      </c>
+      <c r="E58" s="3">
         <v>483622000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>446906000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>508428000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>478451000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>425033000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>495274000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>472089000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>440428000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>369483000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>393328000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>391066000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>420895000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>238258000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>237843000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>237482000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>246843000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>224926000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>229253000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>243549000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>236733000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
@@ -6053,211 +6186,217 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>210955000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>237369000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>233390000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>205510000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>228704000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>243242000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>248579000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>226729000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>250254000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>262512000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>238190000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>213161000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>129833000</v>
+      </c>
+      <c r="E59" s="3">
         <v>105996000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>117322000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>107426000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>105470000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>92543000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>98316000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100345000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>114326000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95530000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>102820000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>97818000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>104445000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>224073000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>224615000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>214522000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>219625000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200419000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>191572000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>184607000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>193563000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>181799000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>175960000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>175302000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>183029000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>182798000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>172286000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>168658000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>173681000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>165026000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>170138000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>152010000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>150615000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>152123000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>157670000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>150925000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>142051000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>147369000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>141634000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2887269000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2820718000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2779947000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2829216000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2755923000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2670625000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2720761000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2671973000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2690866000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2571665000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2565686000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2548220000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2628052000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6333,169 +6472,175 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>306835000</v>
+      </c>
+      <c r="E61" s="3">
         <v>283450000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>317076000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>310844000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>295388000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>292414000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>304412000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>289511000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>286608000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>311986000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>296888000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>288111000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>284228000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>259610000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>267368000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>269623000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>270553000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>270983000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>276282000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>265883000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>235050000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>260968000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>255616000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>261530000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>253601000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>216602000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>236167000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>238011000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>233929000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>229392000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>211842000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>201531000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>197975000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>183208000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>220247000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>203413000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>188974000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>216823000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>216895000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2672000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2541000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1483000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2532000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2664000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2608000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2620000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2777000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3155000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3452000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3548000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2181000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6571,8 +6716,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3195518000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3108495000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3099564000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3141543000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3053843000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2967336000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3027781000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2964104000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2980251000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2888505000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2866026000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2839879000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2914461000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2778178000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2803429000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2842488000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2971606000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2899429000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2812982000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2752775000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2695992000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2546703000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2469602000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2476051000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2355036000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2169269000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2157943000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2124484000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2110154000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2089182000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2076675000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2027454000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2062254000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2014088000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2011437000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1983542000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1979548000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1921872000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1925231000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,34 +7492,37 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>25992000</v>
+        <v>24996000</v>
       </c>
       <c r="E70" s="3">
         <v>25992000</v>
       </c>
       <c r="F70" s="3">
+        <v>25992000</v>
+      </c>
+      <c r="G70" s="3">
         <v>23495000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>20499000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>23159000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>24554000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>26548000</v>
-      </c>
-      <c r="K70" s="3">
-        <v>28397000</v>
       </c>
       <c r="L70" s="3">
         <v>28397000</v>
@@ -7373,31 +7540,31 @@
         <v>28397000</v>
       </c>
       <c r="Q70" s="3">
-        <v>29134000</v>
+        <v>28397000</v>
       </c>
       <c r="R70" s="3">
         <v>29134000</v>
       </c>
       <c r="S70" s="3">
+        <v>29134000</v>
+      </c>
+      <c r="T70" s="3">
         <v>27137000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>24708000</v>
-      </c>
-      <c r="U70" s="3">
-        <v>23441000</v>
       </c>
       <c r="V70" s="3">
         <v>23441000</v>
       </c>
       <c r="W70" s="3">
+        <v>23441000</v>
+      </c>
+      <c r="X70" s="3">
         <v>24319000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>24510000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>23427000</v>
       </c>
       <c r="Z70" s="3">
         <v>23427000</v>
@@ -7406,16 +7573,16 @@
         <v>23427000</v>
       </c>
       <c r="AB70" s="3">
+        <v>23427000</v>
+      </c>
+      <c r="AC70" s="3">
         <v>23401000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>23606000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>24689000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>22326000</v>
       </c>
       <c r="AF70" s="3">
         <v>22326000</v>
@@ -7424,19 +7591,19 @@
         <v>22326000</v>
       </c>
       <c r="AH70" s="3">
+        <v>22326000</v>
+      </c>
+      <c r="AI70" s="3">
         <v>23181000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>24672000</v>
-      </c>
-      <c r="AJ70" s="3">
-        <v>22323000</v>
       </c>
       <c r="AK70" s="3">
         <v>22323000</v>
       </c>
       <c r="AL70" s="3">
-        <v>25220000</v>
+        <v>22323000</v>
       </c>
       <c r="AM70" s="3">
         <v>25220000</v>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>25220000</v>
       </c>
+      <c r="AP70" s="3">
+        <v>25220000</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>267765000</v>
+      </c>
+      <c r="E72" s="3">
         <v>261693000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>258141000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>252180000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>247315000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>240753000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>237954000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>233597000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>228902000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>224672000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>223749000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>218397000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>213062000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>207003000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>201957000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>197159000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>192929000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>188064000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>183007000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>177499000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>170082000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>164088000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>160447000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>157578000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>155866000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>156319000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>151183000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>147577000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>141888000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>136314000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>130747000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>125546000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>120298000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>113816000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>113486000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>109628000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>105467000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>101225000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>98303000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>275672000</v>
+      </c>
+      <c r="E76" s="3">
         <v>277251000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>278160000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>276104000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>275082000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>270804000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>271958000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>267344000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>265155000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>263249000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>258667000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>254922000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>251799000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>244800000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>240390000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>239984000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>239480000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>245358000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>249023000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>253678000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>249681000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>248414000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>245423000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>242210000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>241491000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>241409000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>244781000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>246719000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>244684000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>242999000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>239832000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>241035000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>241552000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>244823000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>250136000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>245767000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>242933000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>240975000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>244863000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8584000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7528000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8469000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7116000</v>
       </c>
-      <c r="G81" s="3">
-        <v>7396000</v>
-      </c>
       <c r="H81" s="3">
+        <v>7360000</v>
+      </c>
+      <c r="I81" s="3">
         <v>6506000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6896000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6897000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6674000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3144000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7802000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7408000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8161000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6904000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6579000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5932000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6600000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6773000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7260000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8964000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7560000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5208000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4440000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3284000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3541000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6748000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5272000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7109000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6869000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7039000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6701000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6466000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>6490000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2234000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4959000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4745000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4835000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4251000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>545000</v>
+      </c>
+      <c r="E83" s="3">
         <v>540000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>529000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>524000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>518000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>508000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>497000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>491000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>483000</v>
       </c>
       <c r="L83" s="3">
         <v>483000</v>
       </c>
       <c r="M83" s="3">
+        <v>483000</v>
+      </c>
+      <c r="N83" s="3">
         <v>471000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>472000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>474000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>502000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>491000</v>
       </c>
       <c r="R83" s="3">
         <v>491000</v>
       </c>
       <c r="S83" s="3">
+        <v>491000</v>
+      </c>
+      <c r="T83" s="3">
         <v>494000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>495000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>473000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>469000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>461000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>487000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>476000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>448000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>432000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>439000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>438000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>434000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>418000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>524000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>515000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>513000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>511000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>515000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>523000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>531000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>534000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>549000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41770000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22945000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46874000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9132000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2184000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25914000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37276000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18096000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15539000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32724000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11772000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11786000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11300000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30998000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13154000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5049000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-45430000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>44651000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9795000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9311000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-52328000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>54594000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-32638000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3006000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>19043000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>59103000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5702000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6725000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>15101000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-13922000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>19606000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-6518000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>40354000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-7048000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>20471000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>9826000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-12846000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-8356000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,8 +9661,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9483,8 +9703,8 @@
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9561,8 +9781,11 @@
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-66451000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1172000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1943000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56918000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89010000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>9410000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27258000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1523000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-71322000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64183000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59934000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>57884000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>30846000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14380000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>34761000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>16738000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-68408000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-58907000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32698000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-108606000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-113080000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-53882000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>54977000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-88349000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-90411000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-43279000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-30133000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2451000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24317000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-26282000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1980000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-22849000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-11917000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-15699000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-9984000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-13941000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-143000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-32510000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,8 +10193,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10002,86 +10235,89 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1877000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1213000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2222000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1725000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1714000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1624000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1566000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1584000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1614000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1848000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-464000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1696000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1926000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1674000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1576000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1148000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1163000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1178000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10679,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>35915000</v>
+      </c>
+      <c r="E100" s="3">
         <v>10047000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-67990000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>55059000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>72832000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36768000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>36779000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8300000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>68658000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>11291000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>27628000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-71695000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>126121000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-24385000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-37889000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-84651000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>40886000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>83040000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>43663000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>51320000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>113627000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>77938000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-12398000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>129132000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>161147000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11866000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>22828000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>7923000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-15508000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>30556000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>21045000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-27085000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>28602000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3843000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>8658000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-9637000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>46404000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>15157000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>3860000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4031000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2712000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1045000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1466000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1515000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-640000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>348000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4234000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4234000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3052000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2970000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1335000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-417000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-936000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>526000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2581000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>807000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1719000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1179000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-949000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>508000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1293000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1024000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-607000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>229000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-710000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1419000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>227000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>414000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>651000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>813000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-2354000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>351000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10634000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14662000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19504000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7568000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16535000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5475000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25043000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7228000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19669000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18653000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21827000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2665000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>146015000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25227000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6974000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-75932000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-74287000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>68367000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19824000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-66071000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-54362000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>79457000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11660000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>38956000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>88830000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4466000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14300000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-229000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5781000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-7454000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13659000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-33042000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>46807000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-14947000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>13677000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9321000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>20287000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4304000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-27773000</v>
       </c>
     </row>
